--- a/src/assets/estimate-template.xlsx
+++ b/src/assets/estimate-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ICTMaintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE81C745-C336-49D6-93F8-B4A74FCB568E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68088DC-45E8-4784-8270-582DC79C8087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="견적서" sheetId="1" r:id="rId1"/>
@@ -437,12 +437,12 @@
     <numFmt numFmtId="176" formatCode="yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;"/>
     <numFmt numFmtId="177" formatCode="&quot;₩&quot;#,##0"/>
     <numFmt numFmtId="178" formatCode="&quot;₩&quot;#,##0_);[Red]\(&quot;₩&quot;#,##0\)"/>
-    <numFmt numFmtId="180" formatCode="#,###&quot;㎡&quot;"/>
-    <numFmt numFmtId="182" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="183" formatCode="&quot;직접인건비의 &quot;0%"/>
-    <numFmt numFmtId="184" formatCode="&quot;총&quot;\ #&quot;종&quot;"/>
-    <numFmt numFmtId="189" formatCode="#,##0_);[Red]\(#,##0\)"/>
-    <numFmt numFmtId="191" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="179" formatCode="#,###&quot;㎡&quot;"/>
+    <numFmt numFmtId="180" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="181" formatCode="&quot;직접인건비의 &quot;0%"/>
+    <numFmt numFmtId="182" formatCode="&quot;총&quot;\ #&quot;종&quot;"/>
+    <numFmt numFmtId="183" formatCode="#,##0_);[Red]\(#,##0\)"/>
+    <numFmt numFmtId="184" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="32">
     <font>
@@ -1091,7 +1091,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1126,7 +1126,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="19" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="19" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
@@ -1141,9 +1141,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1156,13 +1153,13 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="26" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="26" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="25" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="25" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="24" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1189,7 +1186,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="18" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="18" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="6" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1222,6 +1219,128 @@
     <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="25" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="24" fillId="5" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="28" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="184" fontId="24" fillId="6" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="24" fillId="6" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1285,129 +1404,70 @@
     <xf numFmtId="178" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="5" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="5" borderId="22" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="5" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="18" fillId="5" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="5" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="5" borderId="22" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="25" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1418,69 +1478,6 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="8" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="24" fillId="5" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="189" fontId="28" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="191" fontId="24" fillId="6" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="24" fillId="6" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1808,43 +1805,60 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
+      <xdr:colOff>95250</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>57151</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1171575</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>7727</xdr:rowOff>
+      <xdr:colOff>933450</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>185091</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3">
+        <xdr:cNvPr id="2" name="그림 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E47123BE-DD00-40E9-BCF2-BADAC029C663}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6D647B6-39F0-4435-AED1-36B0A6CAC5D5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill rotWithShape="1">
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
-      <xdr:spPr>
+      <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="133350" y="57151"/>
-          <a:ext cx="2228850" cy="426826"/>
+          <a:off x="95250" y="57150"/>
+          <a:ext cx="2028825" cy="366066"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -2757,14 +2771,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.2" customHeight="1">
-      <c r="A1" s="67"/>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="69"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="66"/>
+      <c r="A1" s="68"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="67"/>
       <c r="I1" s="2"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -2799,10 +2813,10 @@
       <c r="D3" s="77" t="s">
         <v>92</v>
       </c>
-      <c r="E3" s="126"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="128"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="80"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -2814,10 +2828,10 @@
       <c r="B4" s="75"/>
       <c r="C4" s="75"/>
       <c r="D4" s="77"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="128"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="80"/>
       <c r="I4" s="4"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -2829,12 +2843,12 @@
       <c r="B5" s="75"/>
       <c r="C5" s="75"/>
       <c r="D5" s="77"/>
-      <c r="E5" s="78" t="s">
+      <c r="E5" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="80"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="56"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
@@ -2842,20 +2856,20 @@
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70" t="s">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53" t="s">
         <v>72</v>
       </c>
-      <c r="D6" s="70"/>
-      <c r="E6" s="85" t="s">
+      <c r="D6" s="53"/>
+      <c r="E6" s="84" t="s">
         <v>73</v>
       </c>
-      <c r="F6" s="78"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="86"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="57"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
@@ -2863,20 +2877,20 @@
       <c r="M6" s="5"/>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A7" s="84" t="s">
+      <c r="A7" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70" t="s">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="70"/>
-      <c r="E7" s="78" t="s">
+      <c r="D7" s="53"/>
+      <c r="E7" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="F7" s="79"/>
-      <c r="G7" s="79"/>
-      <c r="H7" s="80"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="56"/>
       <c r="I7"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -2884,20 +2898,20 @@
       <c r="M7" s="5"/>
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="70"/>
+      <c r="B8" s="53"/>
       <c r="C8" s="71" t="s">
         <v>71</v>
       </c>
       <c r="D8" s="71"/>
-      <c r="E8" s="78" t="s">
+      <c r="E8" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="78"/>
-      <c r="G8" s="78"/>
-      <c r="H8" s="86"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="57"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -2905,10 +2919,10 @@
       <c r="M8" s="5"/>
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A9" s="84" t="s">
+      <c r="A9" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="70"/>
+      <c r="B9" s="53"/>
       <c r="C9" s="72" t="s">
         <v>78</v>
       </c>
@@ -2924,19 +2938,19 @@
       <c r="M9" s="5"/>
     </row>
     <row r="10" spans="1:14" ht="39.6" customHeight="1">
-      <c r="A10" s="84" t="s">
+      <c r="A10" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="70"/>
-      <c r="C10" s="129">
+      <c r="B10" s="53"/>
+      <c r="C10" s="63">
         <f>ROUNDDOWN(G28,3)</f>
         <v>65511468</v>
       </c>
-      <c r="D10" s="130"/>
-      <c r="E10" s="130"/>
-      <c r="F10" s="130"/>
-      <c r="G10" s="130"/>
-      <c r="H10" s="131"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="65"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -2945,16 +2959,16 @@
       <c r="N10" s="3"/>
     </row>
     <row r="11" spans="1:14" ht="40.9" customHeight="1" thickBot="1">
-      <c r="A11" s="89" t="s">
+      <c r="A11" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="90"/>
-      <c r="C11" s="90"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="90"/>
-      <c r="F11" s="90"/>
-      <c r="G11" s="90"/>
-      <c r="H11" s="91"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="62"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -2963,10 +2977,10 @@
       <c r="N11" s="3"/>
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A12" s="87" t="s">
+      <c r="A12" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="88"/>
+      <c r="B12" s="59"/>
       <c r="C12" s="9" t="s">
         <v>9</v>
       </c>
@@ -2991,10 +3005,10 @@
       <c r="M12" s="5"/>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="53"/>
+      <c r="B13" s="94"/>
       <c r="C13" s="12">
         <v>29984.71</v>
       </c>
@@ -3018,10 +3032,10 @@
       <c r="M13" s="5"/>
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A14" s="52" t="s">
+      <c r="A14" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="53"/>
+      <c r="B14" s="94"/>
       <c r="C14" s="12">
         <v>29984.71</v>
       </c>
@@ -3045,10 +3059,10 @@
       <c r="M14" s="5"/>
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A15" s="52" t="s">
+      <c r="A15" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="53"/>
+      <c r="B15" s="94"/>
       <c r="C15" s="12">
         <v>29984.71</v>
       </c>
@@ -3072,16 +3086,16 @@
       <c r="M15" s="5"/>
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A16" s="54" t="s">
+      <c r="A16" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="56"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="96"/>
+      <c r="F16" s="96"/>
+      <c r="G16" s="96"/>
+      <c r="H16" s="97"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -3089,16 +3103,16 @@
       <c r="M16" s="5"/>
     </row>
     <row r="17" spans="1:13" s="1" customFormat="1" ht="8.4499999999999993" customHeight="1">
-      <c r="A17" s="57" t="s">
+      <c r="A17" s="98" t="s">
         <v>65</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="59"/>
+      <c r="B17" s="99"/>
+      <c r="C17" s="99"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="100"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -3106,14 +3120,14 @@
       <c r="M17" s="5"/>
     </row>
     <row r="18" spans="1:13" s="1" customFormat="1" ht="6.6" customHeight="1">
-      <c r="A18" s="60"/>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="59"/>
+      <c r="A18" s="101"/>
+      <c r="B18" s="99"/>
+      <c r="C18" s="99"/>
+      <c r="D18" s="99"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="99"/>
+      <c r="H18" s="100"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
@@ -3121,14 +3135,14 @@
       <c r="M18" s="5"/>
     </row>
     <row r="19" spans="1:13" s="1" customFormat="1" ht="12" customHeight="1">
-      <c r="A19" s="60"/>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="59"/>
+      <c r="A19" s="101"/>
+      <c r="B19" s="99"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="99"/>
+      <c r="H19" s="100"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
@@ -3136,14 +3150,14 @@
       <c r="M19" s="5"/>
     </row>
     <row r="20" spans="1:13" s="1" customFormat="1" ht="53.25" customHeight="1">
-      <c r="A20" s="60"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="59"/>
+      <c r="A20" s="101"/>
+      <c r="B20" s="99"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="99"/>
+      <c r="H20" s="100"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
@@ -3151,14 +3165,14 @@
       <c r="M20" s="5"/>
     </row>
     <row r="21" spans="1:13" s="1" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A21" s="60"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="59"/>
+      <c r="A21" s="101"/>
+      <c r="B21" s="99"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="99"/>
+      <c r="H21" s="100"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
@@ -3166,14 +3180,14 @@
       <c r="M21" s="5"/>
     </row>
     <row r="22" spans="1:13" s="1" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A22" s="60"/>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="59"/>
+      <c r="A22" s="101"/>
+      <c r="B22" s="99"/>
+      <c r="C22" s="99"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="99"/>
+      <c r="G22" s="99"/>
+      <c r="H22" s="100"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
@@ -3181,14 +3195,14 @@
       <c r="M22" s="5"/>
     </row>
     <row r="23" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A23" s="60"/>
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="59"/>
+      <c r="A23" s="101"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="99"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="99"/>
+      <c r="G23" s="99"/>
+      <c r="H23" s="100"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -3196,19 +3210,19 @@
       <c r="M23" s="5"/>
     </row>
     <row r="24" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A24" s="61" t="s">
+      <c r="A24" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-      <c r="E24" s="62"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="63">
+      <c r="B24" s="103"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="103"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="104">
         <f>SUM(G13:G15)</f>
         <v>59555880</v>
       </c>
-      <c r="H24" s="64"/>
+      <c r="H24" s="105"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
@@ -3216,18 +3230,18 @@
       <c r="M24" s="5"/>
     </row>
     <row r="25" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A25" s="101" t="s">
+      <c r="A25" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="B25" s="102"/>
-      <c r="C25" s="102"/>
-      <c r="D25" s="102"/>
-      <c r="E25" s="102"/>
-      <c r="F25" s="103"/>
-      <c r="G25" s="104">
+      <c r="B25" s="107"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="107"/>
+      <c r="E25" s="107"/>
+      <c r="F25" s="108"/>
+      <c r="G25" s="109">
         <v>0</v>
       </c>
-      <c r="H25" s="105"/>
+      <c r="H25" s="110"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
@@ -3235,19 +3249,19 @@
       <c r="M25" s="5"/>
     </row>
     <row r="26" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A26" s="48" t="s">
+      <c r="A26" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="49"/>
-      <c r="C26" s="49"/>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="50">
+      <c r="B26" s="90"/>
+      <c r="C26" s="90"/>
+      <c r="D26" s="90"/>
+      <c r="E26" s="90"/>
+      <c r="F26" s="90"/>
+      <c r="G26" s="91">
         <f>G24-(G24*G25)</f>
         <v>59555880</v>
       </c>
-      <c r="H26" s="51"/>
+      <c r="H26" s="92"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
@@ -3255,19 +3269,19 @@
       <c r="M26" s="5"/>
     </row>
     <row r="27" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A27" s="61" t="s">
+      <c r="A27" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="63">
+      <c r="B27" s="103"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="103"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="103"/>
+      <c r="G27" s="104">
         <f>G26*10%</f>
         <v>5955588</v>
       </c>
-      <c r="H27" s="64"/>
+      <c r="H27" s="105"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
@@ -3275,19 +3289,19 @@
       <c r="M27" s="5"/>
     </row>
     <row r="28" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1" thickBot="1">
-      <c r="A28" s="44" t="s">
+      <c r="A28" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="46">
+      <c r="B28" s="86"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="86"/>
+      <c r="G28" s="87">
         <f>G26+G27</f>
         <v>65511468</v>
       </c>
-      <c r="H28" s="47"/>
+      <c r="H28" s="88"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
@@ -3297,13 +3311,21 @@
     <row r="29" spans="1:13" ht="408.75" customHeight="1" thickTop="1"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A17:H23"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="G25:H25"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C7:D7"/>
@@ -3319,21 +3341,13 @@
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A17:H23"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C10:H10"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3369,23 +3383,23 @@
     <row r="1" spans="1:10" ht="18.75" customHeight="1"/>
     <row r="2" spans="1:10" ht="18.75" customHeight="1"/>
     <row r="3" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A3" s="15"/>
-      <c r="B3" s="95" t="s">
+      <c r="A3" s="124" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="17"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="124"/>
       <c r="I3" s="15"/>
       <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:10" ht="12" customHeight="1">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
       <c r="D4" s="16"/>
       <c r="E4" s="16"/>
       <c r="F4" s="16"/>
@@ -3395,89 +3409,89 @@
       <c r="J4" s="16"/>
     </row>
     <row r="5" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="96" t="s">
+      <c r="C5" s="114" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="96"/>
-      <c r="E5" s="35" t="s">
+      <c r="D5" s="114"/>
+      <c r="E5" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="96" t="s">
+      <c r="F5" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="G5" s="96"/>
-      <c r="H5" s="35" t="s">
+      <c r="G5" s="114"/>
+      <c r="H5" s="34" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A6" s="106" t="s">
+      <c r="A6" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="106" t="s">
+      <c r="B6" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="97">
+      <c r="C6" s="125">
         <v>29984.71</v>
       </c>
-      <c r="D6" s="98"/>
-      <c r="E6" s="106" t="s">
+      <c r="D6" s="126"/>
+      <c r="E6" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="F6" s="99">
+      <c r="F6" s="127">
         <v>1.75</v>
       </c>
-      <c r="G6" s="99"/>
-      <c r="H6" s="20"/>
+      <c r="G6" s="127"/>
+      <c r="H6" s="19"/>
     </row>
     <row r="7" spans="1:10" ht="20.25" customHeight="1">
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
     </row>
     <row r="8" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A8" s="92" t="s">
+      <c r="A8" s="116" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="93"/>
-      <c r="C8" s="93"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="36" t="s">
+      <c r="B8" s="117"/>
+      <c r="C8" s="117"/>
+      <c r="D8" s="117"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="35" t="s">
+      <c r="G8" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="35" t="s">
+      <c r="H8" s="34" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A9" s="114" t="s">
+      <c r="A9" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="115" t="s">
+      <c r="B9" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="22" t="s">
+      <c r="C9" s="120"/>
+      <c r="D9" s="120"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="G9" s="116" t="s">
+      <c r="G9" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="H9" s="21"/>
+      <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A10" s="108" t="s">
+      <c r="A10" s="128" t="s">
         <v>26</v>
       </c>
       <c r="B10" s="111" t="s">
@@ -3486,426 +3500,426 @@
       <c r="C10" s="112"/>
       <c r="D10" s="112"/>
       <c r="E10" s="113"/>
-      <c r="F10" s="22">
+      <c r="F10" s="21">
         <v>624275</v>
       </c>
-      <c r="G10" s="23"/>
-      <c r="H10" s="24"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="23"/>
     </row>
     <row r="11" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A11" s="109"/>
+      <c r="A11" s="129"/>
       <c r="B11" s="111" t="s">
         <v>83</v>
       </c>
       <c r="C11" s="112"/>
       <c r="D11" s="112"/>
       <c r="E11" s="113"/>
-      <c r="F11" s="22">
+      <c r="F11" s="21">
         <v>0</v>
       </c>
-      <c r="G11" s="23"/>
-      <c r="H11" s="107"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="44"/>
     </row>
     <row r="12" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A12" s="110"/>
+      <c r="A12" s="130"/>
       <c r="B12" s="111" t="s">
         <v>86</v>
       </c>
       <c r="C12" s="112"/>
       <c r="D12" s="112"/>
       <c r="E12" s="113"/>
-      <c r="F12" s="22">
+      <c r="F12" s="21">
         <v>0</v>
       </c>
-      <c r="G12" s="23"/>
-      <c r="H12" s="107"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="44"/>
     </row>
     <row r="13" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A13" s="96" t="s">
+      <c r="A13" s="114" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="96"/>
-      <c r="C13" s="96"/>
-      <c r="D13" s="96"/>
-      <c r="E13" s="96"/>
-      <c r="F13" s="38">
+      <c r="B13" s="114"/>
+      <c r="C13" s="114"/>
+      <c r="D13" s="114"/>
+      <c r="E13" s="114"/>
+      <c r="F13" s="37">
         <f>SUM(F9:F12)</f>
         <v>624275</v>
       </c>
-      <c r="G13" s="39"/>
-      <c r="H13" s="40"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="39"/>
     </row>
     <row r="14" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="22">
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="21">
         <v>7491305.5770000024</v>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="28">
         <v>1.2</v>
       </c>
-      <c r="H14" s="30"/>
+      <c r="H14" s="29"/>
     </row>
     <row r="15" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A15" s="37" t="s">
+      <c r="A15" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="31">
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="30">
         <v>5493624.0898000021</v>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="28">
         <v>0.4</v>
       </c>
-      <c r="H15" s="30"/>
+      <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A16" s="96" t="s">
+      <c r="A16" s="114" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="96"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="41">
+      <c r="B16" s="114"/>
+      <c r="C16" s="114"/>
+      <c r="D16" s="114"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="40">
         <v>12984929.666800003</v>
       </c>
-      <c r="G16" s="38"/>
-      <c r="H16" s="42"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="41"/>
     </row>
     <row r="17" spans="1:8" ht="27" customHeight="1">
-      <c r="A17" s="100" t="s">
+      <c r="A17" s="115" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="100"/>
-      <c r="C17" s="100"/>
-      <c r="D17" s="100"/>
-      <c r="E17" s="100"/>
-      <c r="F17" s="25">
+      <c r="B17" s="115"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="115"/>
+      <c r="F17" s="24">
         <v>19851959.779050007</v>
       </c>
-      <c r="G17" s="26"/>
-      <c r="H17" s="34" t="s">
+      <c r="G17" s="25"/>
+      <c r="H17" s="33" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="13.5" customHeight="1"/>
     <row r="19" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="H19" s="33"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="H19" s="32"/>
     </row>
     <row r="20" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="92" t="s">
+      <c r="B20" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="94"/>
-      <c r="F20" s="35" t="s">
+      <c r="C20" s="117"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="H20" s="43" t="s">
+      <c r="H20" s="42" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A21" s="96" t="s">
+      <c r="A21" s="114" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="119" t="s">
+      <c r="B21" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="119"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="119"/>
-      <c r="F21" s="120" t="s">
+      <c r="C21" s="122"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G21" s="121"/>
-      <c r="H21" s="123"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="49"/>
     </row>
     <row r="22" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A22" s="96"/>
-      <c r="B22" s="119" t="s">
+      <c r="A22" s="114"/>
+      <c r="B22" s="122" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="119"/>
-      <c r="D22" s="119"/>
-      <c r="E22" s="119"/>
-      <c r="F22" s="120" t="s">
+      <c r="C22" s="122"/>
+      <c r="D22" s="122"/>
+      <c r="E22" s="122"/>
+      <c r="F22" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G22" s="121"/>
-      <c r="H22" s="123"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="49"/>
     </row>
     <row r="23" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A23" s="96"/>
-      <c r="B23" s="119" t="s">
+      <c r="A23" s="114"/>
+      <c r="B23" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="119"/>
-      <c r="D23" s="119"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="120" t="s">
+      <c r="C23" s="122"/>
+      <c r="D23" s="122"/>
+      <c r="E23" s="122"/>
+      <c r="F23" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G23" s="121"/>
-      <c r="H23" s="123"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="49"/>
     </row>
     <row r="24" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A24" s="96"/>
-      <c r="B24" s="119" t="s">
+      <c r="A24" s="114"/>
+      <c r="B24" s="122" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="119"/>
-      <c r="D24" s="119"/>
-      <c r="E24" s="119"/>
-      <c r="F24" s="120" t="s">
+      <c r="C24" s="122"/>
+      <c r="D24" s="122"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G24" s="121"/>
-      <c r="H24" s="123"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="49"/>
     </row>
     <row r="25" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A25" s="96"/>
-      <c r="B25" s="119" t="s">
+      <c r="A25" s="114"/>
+      <c r="B25" s="122" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="119"/>
-      <c r="D25" s="119"/>
-      <c r="E25" s="119"/>
-      <c r="F25" s="120" t="s">
+      <c r="C25" s="122"/>
+      <c r="D25" s="122"/>
+      <c r="E25" s="122"/>
+      <c r="F25" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G25" s="121"/>
-      <c r="H25" s="123"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="49"/>
     </row>
     <row r="26" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A26" s="96"/>
-      <c r="B26" s="119" t="s">
+      <c r="A26" s="114"/>
+      <c r="B26" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="119"/>
-      <c r="D26" s="119"/>
-      <c r="E26" s="119"/>
-      <c r="F26" s="120" t="s">
+      <c r="C26" s="122"/>
+      <c r="D26" s="122"/>
+      <c r="E26" s="122"/>
+      <c r="F26" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G26" s="121"/>
-      <c r="H26" s="123"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="49"/>
     </row>
     <row r="27" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A27" s="96"/>
-      <c r="B27" s="119" t="s">
+      <c r="A27" s="114"/>
+      <c r="B27" s="122" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="119"/>
-      <c r="D27" s="119"/>
-      <c r="E27" s="119"/>
-      <c r="F27" s="120" t="s">
+      <c r="C27" s="122"/>
+      <c r="D27" s="122"/>
+      <c r="E27" s="122"/>
+      <c r="F27" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G27" s="121"/>
-      <c r="H27" s="123"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="49"/>
     </row>
     <row r="28" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A28" s="96"/>
-      <c r="B28" s="119" t="s">
+      <c r="A28" s="114"/>
+      <c r="B28" s="122" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="119"/>
-      <c r="D28" s="119"/>
-      <c r="E28" s="119"/>
-      <c r="F28" s="120" t="s">
+      <c r="C28" s="122"/>
+      <c r="D28" s="122"/>
+      <c r="E28" s="122"/>
+      <c r="F28" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G28" s="121"/>
-      <c r="H28" s="123"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="49"/>
     </row>
     <row r="29" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A29" s="35" t="s">
+      <c r="A29" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="B29" s="119" t="s">
+      <c r="B29" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="119"/>
-      <c r="D29" s="119"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="120" t="s">
+      <c r="C29" s="122"/>
+      <c r="D29" s="122"/>
+      <c r="E29" s="122"/>
+      <c r="F29" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G29" s="121"/>
-      <c r="H29" s="123"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="49"/>
     </row>
     <row r="30" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A30" s="96" t="s">
+      <c r="A30" s="114" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="119" t="s">
+      <c r="B30" s="122" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="119"/>
-      <c r="D30" s="119"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="120" t="s">
+      <c r="C30" s="122"/>
+      <c r="D30" s="122"/>
+      <c r="E30" s="122"/>
+      <c r="F30" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G30" s="121"/>
-      <c r="H30" s="123"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="49"/>
     </row>
     <row r="31" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A31" s="96"/>
-      <c r="B31" s="119" t="s">
+      <c r="A31" s="114"/>
+      <c r="B31" s="122" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="119"/>
-      <c r="D31" s="119"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="120" t="s">
+      <c r="C31" s="122"/>
+      <c r="D31" s="122"/>
+      <c r="E31" s="122"/>
+      <c r="F31" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G31" s="121"/>
-      <c r="H31" s="123"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="49"/>
     </row>
     <row r="32" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A32" s="96"/>
-      <c r="B32" s="119" t="s">
+      <c r="A32" s="114"/>
+      <c r="B32" s="122" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="119"/>
-      <c r="D32" s="119"/>
-      <c r="E32" s="119"/>
-      <c r="F32" s="120" t="s">
+      <c r="C32" s="122"/>
+      <c r="D32" s="122"/>
+      <c r="E32" s="122"/>
+      <c r="F32" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G32" s="121"/>
-      <c r="H32" s="123"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="49"/>
     </row>
     <row r="33" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A33" s="96"/>
-      <c r="B33" s="119" t="s">
+      <c r="A33" s="114"/>
+      <c r="B33" s="122" t="s">
         <v>56</v>
       </c>
-      <c r="C33" s="119"/>
-      <c r="D33" s="119"/>
-      <c r="E33" s="119"/>
-      <c r="F33" s="120" t="s">
+      <c r="C33" s="122"/>
+      <c r="D33" s="122"/>
+      <c r="E33" s="122"/>
+      <c r="F33" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G33" s="121"/>
-      <c r="H33" s="123"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="49"/>
     </row>
     <row r="34" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A34" s="96"/>
-      <c r="B34" s="119" t="s">
+      <c r="A34" s="114"/>
+      <c r="B34" s="122" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="119"/>
-      <c r="D34" s="119"/>
-      <c r="E34" s="119"/>
-      <c r="F34" s="120" t="s">
+      <c r="C34" s="122"/>
+      <c r="D34" s="122"/>
+      <c r="E34" s="122"/>
+      <c r="F34" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G34" s="121"/>
-      <c r="H34" s="123"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="49"/>
     </row>
     <row r="35" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A35" s="96"/>
-      <c r="B35" s="119" t="s">
+      <c r="A35" s="114"/>
+      <c r="B35" s="122" t="s">
         <v>58</v>
       </c>
-      <c r="C35" s="119"/>
-      <c r="D35" s="119"/>
-      <c r="E35" s="119"/>
-      <c r="F35" s="120" t="s">
+      <c r="C35" s="122"/>
+      <c r="D35" s="122"/>
+      <c r="E35" s="122"/>
+      <c r="F35" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G35" s="121"/>
-      <c r="H35" s="123"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="49"/>
     </row>
     <row r="36" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A36" s="96"/>
-      <c r="B36" s="122" t="s">
+      <c r="A36" s="114"/>
+      <c r="B36" s="123" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="122"/>
-      <c r="D36" s="122"/>
-      <c r="E36" s="122"/>
-      <c r="F36" s="120" t="s">
+      <c r="C36" s="123"/>
+      <c r="D36" s="123"/>
+      <c r="E36" s="123"/>
+      <c r="F36" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G36" s="121"/>
-      <c r="H36" s="123"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="49"/>
     </row>
     <row r="37" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A37" s="96" t="s">
+      <c r="A37" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="B37" s="119" t="s">
+      <c r="B37" s="122" t="s">
         <v>50</v>
       </c>
-      <c r="C37" s="119"/>
-      <c r="D37" s="119"/>
-      <c r="E37" s="119"/>
-      <c r="F37" s="120" t="s">
+      <c r="C37" s="122"/>
+      <c r="D37" s="122"/>
+      <c r="E37" s="122"/>
+      <c r="F37" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G37" s="121"/>
-      <c r="H37" s="123"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="49"/>
     </row>
     <row r="38" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A38" s="96"/>
-      <c r="B38" s="119" t="s">
+      <c r="A38" s="114"/>
+      <c r="B38" s="122" t="s">
         <v>51</v>
       </c>
-      <c r="C38" s="119"/>
-      <c r="D38" s="119"/>
-      <c r="E38" s="119"/>
-      <c r="F38" s="120" t="s">
+      <c r="C38" s="122"/>
+      <c r="D38" s="122"/>
+      <c r="E38" s="122"/>
+      <c r="F38" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="G38" s="121"/>
-      <c r="H38" s="123"/>
+      <c r="G38" s="48"/>
+      <c r="H38" s="49"/>
     </row>
     <row r="39" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A39" s="125" t="s">
+      <c r="A39" s="51" t="s">
         <v>88</v>
       </c>
-      <c r="B39" s="100" t="s">
+      <c r="B39" s="115" t="s">
         <v>89</v>
       </c>
-      <c r="C39" s="100"/>
-      <c r="D39" s="100"/>
-      <c r="E39" s="100"/>
-      <c r="F39" s="100"/>
-      <c r="G39" s="124">
+      <c r="C39" s="115"/>
+      <c r="D39" s="115"/>
+      <c r="E39" s="115"/>
+      <c r="F39" s="115"/>
+      <c r="G39" s="50">
         <f>SUM(G21:G38)</f>
         <v>0</v>
       </c>
-      <c r="H39" s="26">
+      <c r="H39" s="25">
         <f>SUM(H21:H38)</f>
         <v>0</v>
       </c>
@@ -3915,11 +3929,11 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A3:H3"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B37:E37"/>
@@ -3936,6 +3950,11 @@
     <mergeCell ref="A21:A28"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
@@ -3943,11 +3962,6 @@
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="F6:G6"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>

--- a/src/assets/estimate-template.xlsx
+++ b/src/assets/estimate-template.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ICTMaintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D68088DC-45E8-4784-8270-582DC79C8087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F8409D-1965-4D62-BF8C-88584971DDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11655" yWindow="960" windowWidth="16920" windowHeight="19845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="견적서" sheetId="1" r:id="rId1"/>
     <sheet name="세부내역" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">세부내역!$A$19:$H$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">세부내역!$A$19:$H$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">견적서!$A$1:$H$28</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">세부내역!$A$1:$H$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">세부내역!$A$1:$H$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="79">
   <si>
     <t xml:space="preserve"> 발급일(Date)</t>
   </si>
@@ -190,34 +190,6 @@
     <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
-    <t>배관설비</t>
-    <phoneticPr fontId="22" type="noConversion"/>
-  </si>
-  <si>
-    <t>국선인입설비</t>
-    <phoneticPr fontId="22" type="noConversion"/>
-  </si>
-  <si>
-    <t>단자함설비</t>
-    <phoneticPr fontId="22" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동통신구내선로설비</t>
-    <phoneticPr fontId="22" type="noConversion"/>
-  </si>
-  <si>
-    <t>전화설비</t>
-    <phoneticPr fontId="22" type="noConversion"/>
-  </si>
-  <si>
-    <t>방송 공동수신 안테나 시설</t>
-    <phoneticPr fontId="22" type="noConversion"/>
-  </si>
-  <si>
-    <t>종합유선방송 구내전송선로설비</t>
-    <phoneticPr fontId="22" type="noConversion"/>
-  </si>
-  <si>
     <t>방 송 설 비</t>
     <phoneticPr fontId="22" type="noConversion"/>
   </si>
@@ -234,34 +206,11 @@
     <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
-    <t>통신접지설비</t>
-    <phoneticPr fontId="22" type="noConversion"/>
-  </si>
-  <si>
     <t>정 보 설 비</t>
     <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <t>네트워크설비</t>
-  </si>
-  <si>
-    <t>전자출입(통제)시스템</t>
-  </si>
-  <si>
-    <t>원격검침시스템</t>
-  </si>
-  <si>
-    <t>주차관제시스템</t>
-  </si>
-  <si>
-    <t>영상정보처리기기 시스템</t>
-  </si>
-  <si>
-    <t>전기시계시스템</t>
-  </si>
-  <si>
-    <t>시설관리시스템 (Facility Management System)</t>
-    <phoneticPr fontId="22" type="noConversion"/>
   </si>
   <si>
     <t>수  량</t>
@@ -411,10 +360,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>18건</t>
-    <phoneticPr fontId="22" type="noConversion"/>
-  </si>
-  <si>
     <t>기준인원 합계</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -425,6 +370,10 @@
   <si>
     <t>귀중</t>
     <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>건</t>
+    <phoneticPr fontId="22" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1091,7 +1040,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1246,10 +1195,187 @@
     <xf numFmtId="41" fontId="24" fillId="6" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="5" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="8" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="5" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="5" borderId="22" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1261,6 +1387,17 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1287,197 +1424,6 @@
     </xf>
     <xf numFmtId="5" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="5" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="5" borderId="22" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="5" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="8" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2771,14 +2717,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.2" customHeight="1">
-      <c r="A1" s="68"/>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="67"/>
+      <c r="A1" s="99"/>
+      <c r="B1" s="100"/>
+      <c r="C1" s="100"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="98"/>
       <c r="I1" s="2"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -2787,16 +2733,16 @@
       <c r="N1" s="3"/>
     </row>
     <row r="2" spans="1:14" ht="43.5" customHeight="1">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="116" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="83"/>
+      <c r="B2" s="117"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="118"/>
       <c r="I2" s="2"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -2805,18 +2751,18 @@
       <c r="N2" s="3"/>
     </row>
     <row r="3" spans="1:14" ht="34.9" customHeight="1">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="106" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="107"/>
+      <c r="C3" s="107"/>
+      <c r="D3" s="109" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="77" t="s">
-        <v>92</v>
-      </c>
-      <c r="E3" s="78"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="80"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="111"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="112"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -2824,14 +2770,14 @@
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:14" ht="34.9" customHeight="1">
-      <c r="A4" s="76"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="80"/>
+      <c r="A4" s="108"/>
+      <c r="B4" s="107"/>
+      <c r="C4" s="107"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="112"/>
       <c r="I4" s="4"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -2839,16 +2785,16 @@
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="34.9" customHeight="1">
-      <c r="A5" s="76"/>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="54" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="56"/>
+      <c r="A5" s="108"/>
+      <c r="B5" s="107"/>
+      <c r="C5" s="107"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="113" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="114"/>
+      <c r="G5" s="114"/>
+      <c r="H5" s="115"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
@@ -2856,20 +2802,20 @@
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="53"/>
-      <c r="E6" s="84" t="s">
-        <v>73</v>
-      </c>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="57"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="102"/>
+      <c r="E6" s="120" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="113"/>
+      <c r="G6" s="113"/>
+      <c r="H6" s="121"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
@@ -2877,20 +2823,20 @@
       <c r="M6" s="5"/>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53" t="s">
-        <v>70</v>
-      </c>
-      <c r="D7" s="53"/>
-      <c r="E7" s="54" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="56"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="102" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="102"/>
+      <c r="E7" s="113" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="114"/>
+      <c r="G7" s="114"/>
+      <c r="H7" s="115"/>
       <c r="I7"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -2898,20 +2844,20 @@
       <c r="M7" s="5"/>
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="119" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="71" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="71"/>
-      <c r="E8" s="54" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="57"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="103" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="103"/>
+      <c r="E8" s="113" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="113"/>
+      <c r="G8" s="113"/>
+      <c r="H8" s="121"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -2919,18 +2865,18 @@
       <c r="M8" s="5"/>
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="53"/>
-      <c r="C9" s="72" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="73"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="104" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="104"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="104"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="105"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -2938,19 +2884,19 @@
       <c r="M9" s="5"/>
     </row>
     <row r="10" spans="1:14" ht="39.6" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="63">
+      <c r="B10" s="102"/>
+      <c r="C10" s="127">
         <f>ROUNDDOWN(G28,3)</f>
         <v>65511468</v>
       </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="65"/>
+      <c r="D10" s="128"/>
+      <c r="E10" s="128"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="128"/>
+      <c r="H10" s="129"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -2959,16 +2905,16 @@
       <c r="N10" s="3"/>
     </row>
     <row r="11" spans="1:14" ht="40.9" customHeight="1" thickBot="1">
-      <c r="A11" s="60" t="s">
+      <c r="A11" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="62"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="125"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="126"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -2977,24 +2923,24 @@
       <c r="N11" s="3"/>
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A12" s="58" t="s">
+      <c r="A12" s="122" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="59"/>
+      <c r="B12" s="123"/>
       <c r="C12" s="9" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>7</v>
@@ -3005,10 +2951,10 @@
       <c r="M12" s="5"/>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A13" s="93" t="s">
+      <c r="A13" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="94"/>
+      <c r="B13" s="80"/>
       <c r="C13" s="12">
         <v>29984.71</v>
       </c>
@@ -3032,10 +2978,10 @@
       <c r="M13" s="5"/>
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A14" s="93" t="s">
+      <c r="A14" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="94"/>
+      <c r="B14" s="80"/>
       <c r="C14" s="12">
         <v>29984.71</v>
       </c>
@@ -3059,10 +3005,10 @@
       <c r="M14" s="5"/>
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A15" s="93" t="s">
+      <c r="A15" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="94"/>
+      <c r="B15" s="80"/>
       <c r="C15" s="12">
         <v>29984.71</v>
       </c>
@@ -3086,16 +3032,16 @@
       <c r="M15" s="5"/>
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A16" s="95" t="s">
+      <c r="A16" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="96"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="97"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="82"/>
+      <c r="F16" s="82"/>
+      <c r="G16" s="82"/>
+      <c r="H16" s="83"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -3103,16 +3049,16 @@
       <c r="M16" s="5"/>
     </row>
     <row r="17" spans="1:13" s="1" customFormat="1" ht="8.4499999999999993" customHeight="1">
-      <c r="A17" s="98" t="s">
-        <v>65</v>
-      </c>
-      <c r="B17" s="99"/>
-      <c r="C17" s="99"/>
-      <c r="D17" s="99"/>
-      <c r="E17" s="99"/>
-      <c r="F17" s="99"/>
-      <c r="G17" s="99"/>
-      <c r="H17" s="100"/>
+      <c r="A17" s="84" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" s="85"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="85"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="86"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -3120,14 +3066,14 @@
       <c r="M17" s="5"/>
     </row>
     <row r="18" spans="1:13" s="1" customFormat="1" ht="6.6" customHeight="1">
-      <c r="A18" s="101"/>
-      <c r="B18" s="99"/>
-      <c r="C18" s="99"/>
-      <c r="D18" s="99"/>
-      <c r="E18" s="99"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="99"/>
-      <c r="H18" s="100"/>
+      <c r="A18" s="87"/>
+      <c r="B18" s="85"/>
+      <c r="C18" s="85"/>
+      <c r="D18" s="85"/>
+      <c r="E18" s="85"/>
+      <c r="F18" s="85"/>
+      <c r="G18" s="85"/>
+      <c r="H18" s="86"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
@@ -3135,14 +3081,14 @@
       <c r="M18" s="5"/>
     </row>
     <row r="19" spans="1:13" s="1" customFormat="1" ht="12" customHeight="1">
-      <c r="A19" s="101"/>
-      <c r="B19" s="99"/>
-      <c r="C19" s="99"/>
-      <c r="D19" s="99"/>
-      <c r="E19" s="99"/>
-      <c r="F19" s="99"/>
-      <c r="G19" s="99"/>
-      <c r="H19" s="100"/>
+      <c r="A19" s="87"/>
+      <c r="B19" s="85"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="85"/>
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="86"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
@@ -3150,14 +3096,14 @@
       <c r="M19" s="5"/>
     </row>
     <row r="20" spans="1:13" s="1" customFormat="1" ht="53.25" customHeight="1">
-      <c r="A20" s="101"/>
-      <c r="B20" s="99"/>
-      <c r="C20" s="99"/>
-      <c r="D20" s="99"/>
-      <c r="E20" s="99"/>
-      <c r="F20" s="99"/>
-      <c r="G20" s="99"/>
-      <c r="H20" s="100"/>
+      <c r="A20" s="87"/>
+      <c r="B20" s="85"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="85"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="86"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
@@ -3165,14 +3111,14 @@
       <c r="M20" s="5"/>
     </row>
     <row r="21" spans="1:13" s="1" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A21" s="101"/>
-      <c r="B21" s="99"/>
-      <c r="C21" s="99"/>
-      <c r="D21" s="99"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="99"/>
-      <c r="G21" s="99"/>
-      <c r="H21" s="100"/>
+      <c r="A21" s="87"/>
+      <c r="B21" s="85"/>
+      <c r="C21" s="85"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="85"/>
+      <c r="H21" s="86"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
@@ -3180,14 +3126,14 @@
       <c r="M21" s="5"/>
     </row>
     <row r="22" spans="1:13" s="1" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A22" s="101"/>
-      <c r="B22" s="99"/>
-      <c r="C22" s="99"/>
-      <c r="D22" s="99"/>
-      <c r="E22" s="99"/>
-      <c r="F22" s="99"/>
-      <c r="G22" s="99"/>
-      <c r="H22" s="100"/>
+      <c r="A22" s="87"/>
+      <c r="B22" s="85"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="85"/>
+      <c r="E22" s="85"/>
+      <c r="F22" s="85"/>
+      <c r="G22" s="85"/>
+      <c r="H22" s="86"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
@@ -3195,14 +3141,14 @@
       <c r="M22" s="5"/>
     </row>
     <row r="23" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A23" s="101"/>
-      <c r="B23" s="99"/>
-      <c r="C23" s="99"/>
-      <c r="D23" s="99"/>
-      <c r="E23" s="99"/>
-      <c r="F23" s="99"/>
-      <c r="G23" s="99"/>
-      <c r="H23" s="100"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="85"/>
+      <c r="C23" s="85"/>
+      <c r="D23" s="85"/>
+      <c r="E23" s="85"/>
+      <c r="F23" s="85"/>
+      <c r="G23" s="85"/>
+      <c r="H23" s="86"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -3210,19 +3156,19 @@
       <c r="M23" s="5"/>
     </row>
     <row r="24" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A24" s="102" t="s">
+      <c r="A24" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="103"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="103"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="103"/>
-      <c r="G24" s="104">
+      <c r="B24" s="89"/>
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="90">
         <f>SUM(G13:G15)</f>
         <v>59555880</v>
       </c>
-      <c r="H24" s="105"/>
+      <c r="H24" s="91"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
@@ -3230,18 +3176,18 @@
       <c r="M24" s="5"/>
     </row>
     <row r="25" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A25" s="106" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="107"/>
-      <c r="C25" s="107"/>
-      <c r="D25" s="107"/>
-      <c r="E25" s="107"/>
-      <c r="F25" s="108"/>
-      <c r="G25" s="109">
+      <c r="A25" s="92" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="93"/>
+      <c r="C25" s="93"/>
+      <c r="D25" s="93"/>
+      <c r="E25" s="93"/>
+      <c r="F25" s="94"/>
+      <c r="G25" s="95">
         <v>0</v>
       </c>
-      <c r="H25" s="110"/>
+      <c r="H25" s="96"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
@@ -3249,19 +3195,19 @@
       <c r="M25" s="5"/>
     </row>
     <row r="26" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A26" s="89" t="s">
+      <c r="A26" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="90"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="90"/>
-      <c r="E26" s="90"/>
-      <c r="F26" s="90"/>
-      <c r="G26" s="91">
+      <c r="B26" s="76"/>
+      <c r="C26" s="76"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="77">
         <f>G24-(G24*G25)</f>
         <v>59555880</v>
       </c>
-      <c r="H26" s="92"/>
+      <c r="H26" s="78"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
@@ -3269,19 +3215,19 @@
       <c r="M26" s="5"/>
     </row>
     <row r="27" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A27" s="102" t="s">
+      <c r="A27" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="103"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="103"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="103"/>
-      <c r="G27" s="104">
+      <c r="B27" s="89"/>
+      <c r="C27" s="89"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="90">
         <f>G26*10%</f>
         <v>5955588</v>
       </c>
-      <c r="H27" s="105"/>
+      <c r="H27" s="91"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
@@ -3289,19 +3235,19 @@
       <c r="M27" s="5"/>
     </row>
     <row r="28" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1" thickBot="1">
-      <c r="A28" s="85" t="s">
+      <c r="A28" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="86"/>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="87">
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="73">
         <f>G26+G27</f>
         <v>65511468</v>
       </c>
-      <c r="H28" s="88"/>
+      <c r="H28" s="74"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
@@ -3311,6 +3257,28 @@
     <row r="29" spans="1:13" ht="408.75" customHeight="1" thickTop="1"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="A3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:H4"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="A26:F26"/>
@@ -3326,28 +3294,6 @@
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="A3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:H4"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C10:H10"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3364,7 +3310,7 @@
   <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="20.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.88671875" style="13" customWidth="1"/>
@@ -3383,16 +3329,16 @@
     <row r="1" spans="1:10" ht="18.75" customHeight="1"/>
     <row r="2" spans="1:10" ht="18.75" customHeight="1"/>
     <row r="3" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A3" s="124" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="124"/>
-      <c r="H3" s="124"/>
+      <c r="A3" s="56" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
       <c r="I3" s="15"/>
       <c r="J3" s="15"/>
     </row>
@@ -3413,41 +3359,41 @@
         <v>18</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="C5" s="114" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="114"/>
+      <c r="D5" s="52"/>
       <c r="E5" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="114" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="114"/>
+      <c r="F5" s="52" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="52"/>
       <c r="H5" s="34" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="20.25" customHeight="1">
       <c r="A6" s="43" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="B6" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" s="125">
+        <v>66</v>
+      </c>
+      <c r="C6" s="53">
         <v>29984.71</v>
       </c>
-      <c r="D6" s="126"/>
+      <c r="D6" s="54"/>
       <c r="E6" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="F6" s="127">
+        <v>73</v>
+      </c>
+      <c r="F6" s="55">
         <v>1.75</v>
       </c>
-      <c r="G6" s="127"/>
+      <c r="G6" s="55"/>
       <c r="H6" s="19"/>
     </row>
     <row r="7" spans="1:10" ht="20.25" customHeight="1">
@@ -3455,13 +3401,13 @@
       <c r="C7" s="14"/>
     </row>
     <row r="8" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A8" s="116" t="s">
+      <c r="A8" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="117"/>
-      <c r="C8" s="117"/>
-      <c r="D8" s="117"/>
-      <c r="E8" s="118"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="59"/>
       <c r="F8" s="35" t="s">
         <v>22</v>
       </c>
@@ -3476,30 +3422,30 @@
       <c r="A9" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="119" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="121"/>
+      <c r="B9" s="60" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="62"/>
       <c r="F9" s="21" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="G9" s="46" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A10" s="128" t="s">
+      <c r="A10" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="111" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="113"/>
+      <c r="B10" s="64" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="65"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="66"/>
       <c r="F10" s="21">
         <v>624275</v>
       </c>
@@ -3507,13 +3453,13 @@
       <c r="H10" s="23"/>
     </row>
     <row r="11" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A11" s="129"/>
-      <c r="B11" s="111" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="112"/>
-      <c r="D11" s="112"/>
-      <c r="E11" s="113"/>
+      <c r="A11" s="69"/>
+      <c r="B11" s="64" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="66"/>
       <c r="F11" s="21">
         <v>0</v>
       </c>
@@ -3521,13 +3467,13 @@
       <c r="H11" s="44"/>
     </row>
     <row r="12" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A12" s="130"/>
-      <c r="B12" s="111" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="112"/>
-      <c r="D12" s="112"/>
-      <c r="E12" s="113"/>
+      <c r="A12" s="70"/>
+      <c r="B12" s="64" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="66"/>
       <c r="F12" s="21">
         <v>0</v>
       </c>
@@ -3535,13 +3481,13 @@
       <c r="H12" s="44"/>
     </row>
     <row r="13" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A13" s="114" t="s">
+      <c r="A13" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="114"/>
-      <c r="C13" s="114"/>
-      <c r="D13" s="114"/>
-      <c r="E13" s="114"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
       <c r="F13" s="37">
         <f>SUM(F9:F12)</f>
         <v>624275</v>
@@ -3586,13 +3532,13 @@
       <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A16" s="114" t="s">
+      <c r="A16" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="114"/>
-      <c r="C16" s="114"/>
-      <c r="D16" s="114"/>
-      <c r="E16" s="114"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
       <c r="F16" s="40">
         <v>12984929.666800003</v>
       </c>
@@ -3600,25 +3546,25 @@
       <c r="H16" s="41"/>
     </row>
     <row r="17" spans="1:8" ht="27" customHeight="1">
-      <c r="A17" s="115" t="s">
+      <c r="A17" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="115"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
       <c r="F17" s="24">
         <v>19851959.779050007</v>
       </c>
       <c r="G17" s="25"/>
       <c r="H17" s="33" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="13.5" customHeight="1"/>
     <row r="19" spans="1:8" ht="20.25" customHeight="1">
       <c r="A19" s="31" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
@@ -3628,12 +3574,12 @@
       <c r="A20" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="116" t="s">
+      <c r="B20" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="117"/>
-      <c r="D20" s="117"/>
-      <c r="E20" s="118"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="59"/>
       <c r="F20" s="34" t="s">
         <v>36</v>
       </c>
@@ -3641,19 +3587,19 @@
         <v>37</v>
       </c>
       <c r="H20" s="42" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A21" s="114" t="s">
+      <c r="A21" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="122" t="s">
+      <c r="B21" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="122"/>
-      <c r="D21" s="122"/>
-      <c r="E21" s="122"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="63"/>
       <c r="F21" s="47" t="s">
         <v>27</v>
       </c>
@@ -3661,13 +3607,15 @@
       <c r="H21" s="49"/>
     </row>
     <row r="22" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A22" s="114"/>
-      <c r="B22" s="122" t="s">
+      <c r="A22" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="122"/>
-      <c r="D22" s="122"/>
-      <c r="E22" s="122"/>
+      <c r="B22" s="63" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="63"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
       <c r="F22" s="47" t="s">
         <v>27</v>
       </c>
@@ -3675,13 +3623,15 @@
       <c r="H22" s="49"/>
     </row>
     <row r="23" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A23" s="114"/>
-      <c r="B23" s="122" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="122"/>
-      <c r="D23" s="122"/>
-      <c r="E23" s="122"/>
+      <c r="A23" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="63"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="63"/>
       <c r="F23" s="47" t="s">
         <v>27</v>
       </c>
@@ -3689,13 +3639,15 @@
       <c r="H23" s="49"/>
     </row>
     <row r="24" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A24" s="114"/>
-      <c r="B24" s="122" t="s">
+      <c r="A24" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="122"/>
-      <c r="D24" s="122"/>
-      <c r="E24" s="122"/>
+      <c r="B24" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="63"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
       <c r="F24" s="47" t="s">
         <v>27</v>
       </c>
@@ -3703,282 +3655,58 @@
       <c r="H24" s="49"/>
     </row>
     <row r="25" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A25" s="114"/>
-      <c r="B25" s="122" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="122"/>
-      <c r="D25" s="122"/>
-      <c r="E25" s="122"/>
-      <c r="F25" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" s="48"/>
-      <c r="H25" s="49"/>
+      <c r="A25" s="51" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="67" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="67"/>
+      <c r="G25" s="50">
+        <f>SUM(G21:G24)</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="25">
+        <f>SUM(H21:H24)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A26" s="114"/>
-      <c r="B26" s="122" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="122"/>
-      <c r="D26" s="122"/>
-      <c r="E26" s="122"/>
-      <c r="F26" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G26" s="48"/>
-      <c r="H26" s="49"/>
-    </row>
-    <row r="27" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A27" s="114"/>
-      <c r="B27" s="122" t="s">
-        <v>45</v>
-      </c>
-      <c r="C27" s="122"/>
-      <c r="D27" s="122"/>
-      <c r="E27" s="122"/>
-      <c r="F27" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G27" s="48"/>
-      <c r="H27" s="49"/>
-    </row>
-    <row r="28" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A28" s="114"/>
-      <c r="B28" s="122" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" s="122"/>
-      <c r="D28" s="122"/>
-      <c r="E28" s="122"/>
-      <c r="F28" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G28" s="48"/>
-      <c r="H28" s="49"/>
-    </row>
-    <row r="29" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A29" s="34" t="s">
-        <v>47</v>
-      </c>
-      <c r="B29" s="122" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="122"/>
-      <c r="D29" s="122"/>
-      <c r="E29" s="122"/>
-      <c r="F29" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="48"/>
-      <c r="H29" s="49"/>
-    </row>
-    <row r="30" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A30" s="114" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="122" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="122"/>
-      <c r="D30" s="122"/>
-      <c r="E30" s="122"/>
-      <c r="F30" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G30" s="48"/>
-      <c r="H30" s="49"/>
-    </row>
-    <row r="31" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A31" s="114"/>
-      <c r="B31" s="122" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="122"/>
-      <c r="D31" s="122"/>
-      <c r="E31" s="122"/>
-      <c r="F31" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G31" s="48"/>
-      <c r="H31" s="49"/>
-    </row>
-    <row r="32" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A32" s="114"/>
-      <c r="B32" s="122" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" s="122"/>
-      <c r="D32" s="122"/>
-      <c r="E32" s="122"/>
-      <c r="F32" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G32" s="48"/>
-      <c r="H32" s="49"/>
-    </row>
-    <row r="33" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A33" s="114"/>
-      <c r="B33" s="122" t="s">
-        <v>56</v>
-      </c>
-      <c r="C33" s="122"/>
-      <c r="D33" s="122"/>
-      <c r="E33" s="122"/>
-      <c r="F33" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G33" s="48"/>
-      <c r="H33" s="49"/>
-    </row>
-    <row r="34" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A34" s="114"/>
-      <c r="B34" s="122" t="s">
-        <v>57</v>
-      </c>
-      <c r="C34" s="122"/>
-      <c r="D34" s="122"/>
-      <c r="E34" s="122"/>
-      <c r="F34" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G34" s="48"/>
-      <c r="H34" s="49"/>
-    </row>
-    <row r="35" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A35" s="114"/>
-      <c r="B35" s="122" t="s">
-        <v>58</v>
-      </c>
-      <c r="C35" s="122"/>
-      <c r="D35" s="122"/>
-      <c r="E35" s="122"/>
-      <c r="F35" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G35" s="48"/>
-      <c r="H35" s="49"/>
-    </row>
-    <row r="36" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A36" s="114"/>
-      <c r="B36" s="123" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="123"/>
-      <c r="D36" s="123"/>
-      <c r="E36" s="123"/>
-      <c r="F36" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G36" s="48"/>
-      <c r="H36" s="49"/>
-    </row>
-    <row r="37" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A37" s="114" t="s">
-        <v>49</v>
-      </c>
-      <c r="B37" s="122" t="s">
-        <v>50</v>
-      </c>
-      <c r="C37" s="122"/>
-      <c r="D37" s="122"/>
-      <c r="E37" s="122"/>
-      <c r="F37" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G37" s="48"/>
-      <c r="H37" s="49"/>
-    </row>
-    <row r="38" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A38" s="114"/>
-      <c r="B38" s="122" t="s">
-        <v>51</v>
-      </c>
-      <c r="C38" s="122"/>
-      <c r="D38" s="122"/>
-      <c r="E38" s="122"/>
-      <c r="F38" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G38" s="48"/>
-      <c r="H38" s="49"/>
-    </row>
-    <row r="39" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A39" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="B39" s="115" t="s">
-        <v>89</v>
-      </c>
-      <c r="C39" s="115"/>
-      <c r="D39" s="115"/>
-      <c r="E39" s="115"/>
-      <c r="F39" s="115"/>
-      <c r="G39" s="50">
-        <f>SUM(G21:G38)</f>
-        <v>0</v>
-      </c>
-      <c r="H39" s="25">
-        <f>SUM(H21:H38)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="20.25" customHeight="1">
-      <c r="H40" s="14"/>
+      <c r="H26" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="20">
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B21:E21"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="A30:A36"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="A21:A28"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A10:A12"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="H21:H33">
+  <conditionalFormatting sqref="H21:H23">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H34:H36">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H37:H38">
+  <conditionalFormatting sqref="H24">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>TRUE</formula>
     </cfRule>

--- a/src/assets/estimate-template.xlsx
+++ b/src/assets/estimate-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ICTMaintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F8409D-1965-4D62-BF8C-88584971DDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7947033-901C-4A9C-A4BE-4E1B4841B74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11655" yWindow="960" windowWidth="16920" windowHeight="19845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="견적서" sheetId="1" r:id="rId1"/>
@@ -1174,9 +1174,6 @@
     <xf numFmtId="181" fontId="25" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="24" fillId="5" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1195,6 +1192,9 @@
     <xf numFmtId="41" fontId="24" fillId="6" borderId="19" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1244,13 +1244,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="8" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1434,29 +1434,7 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="2" xr:uid="{809DB65C-5395-43CE-B3C7-7F15C1F3DD0A}"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <font>
-        <color rgb="FFFFFFD5"/>
-      </font>
-      <fill>
-        <patternFill>
-          <fgColor rgb="FFFFFFD5"/>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFFD5"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFD5"/>
-          <bgColor rgb="FFFFFFCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <font>
         <color rgb="FFFFFFD5"/>
@@ -1651,22 +1629,22 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="14"/>
+      <tableStyleElement type="headerRow" dxfId="13"/>
+      <tableStyleElement type="totalRow" dxfId="12"/>
+      <tableStyleElement type="firstColumn" dxfId="11"/>
+      <tableStyleElement type="lastColumn" dxfId="10"/>
+      <tableStyleElement type="firstRowStripe" dxfId="9"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="8"/>
     </tableStyle>
     <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" dxfId="9"/>
-      <tableStyleElement type="headerRow" dxfId="8"/>
-      <tableStyleElement type="totalRow" dxfId="7"/>
-      <tableStyleElement type="firstColumn" dxfId="6"/>
-      <tableStyleElement type="lastColumn" dxfId="5"/>
-      <tableStyleElement type="firstRowStripe" dxfId="4"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="3"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -3419,7 +3397,7 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="51" t="s">
         <v>25</v>
       </c>
       <c r="B9" s="60" t="s">
@@ -3431,7 +3409,7 @@
       <c r="F9" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="46" t="s">
+      <c r="G9" s="45" t="s">
         <v>75</v>
       </c>
       <c r="H9" s="20"/>
@@ -3600,11 +3578,11 @@
       <c r="C21" s="63"/>
       <c r="D21" s="63"/>
       <c r="E21" s="63"/>
-      <c r="F21" s="47" t="s">
+      <c r="F21" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="G21" s="48"/>
-      <c r="H21" s="49"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="48"/>
     </row>
     <row r="22" spans="1:8" ht="20.25" customHeight="1">
       <c r="A22" s="34" t="s">
@@ -3616,11 +3594,11 @@
       <c r="C22" s="63"/>
       <c r="D22" s="63"/>
       <c r="E22" s="63"/>
-      <c r="F22" s="47" t="s">
+      <c r="F22" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="G22" s="48"/>
-      <c r="H22" s="49"/>
+      <c r="G22" s="47"/>
+      <c r="H22" s="48"/>
     </row>
     <row r="23" spans="1:8" ht="20.25" customHeight="1">
       <c r="A23" s="34" t="s">
@@ -3632,11 +3610,11 @@
       <c r="C23" s="63"/>
       <c r="D23" s="63"/>
       <c r="E23" s="63"/>
-      <c r="F23" s="47" t="s">
+      <c r="F23" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="G23" s="48"/>
-      <c r="H23" s="49"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="48"/>
     </row>
     <row r="24" spans="1:8" ht="20.25" customHeight="1">
       <c r="A24" s="34" t="s">
@@ -3648,14 +3626,14 @@
       <c r="C24" s="63"/>
       <c r="D24" s="63"/>
       <c r="E24" s="63"/>
-      <c r="F24" s="47" t="s">
+      <c r="F24" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="G24" s="48"/>
-      <c r="H24" s="49"/>
+      <c r="G24" s="47"/>
+      <c r="H24" s="48"/>
     </row>
     <row r="25" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A25" s="51" t="s">
+      <c r="A25" s="50" t="s">
         <v>74</v>
       </c>
       <c r="B25" s="67" t="s">
@@ -3665,7 +3643,7 @@
       <c r="D25" s="67"/>
       <c r="E25" s="67"/>
       <c r="F25" s="67"/>
-      <c r="G25" s="50">
+      <c r="G25" s="49">
         <f>SUM(G21:G24)</f>
         <v>0</v>
       </c>
@@ -3679,21 +3657,21 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B12:E12"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B22:E22"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="C6:D6"/>
@@ -3701,12 +3679,7 @@
     <mergeCell ref="A3:H3"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
-  <conditionalFormatting sqref="H21:H23">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
-      <formula>TRUE</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H24">
+  <conditionalFormatting sqref="H21:H24">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>TRUE</formula>
     </cfRule>

--- a/src/assets/estimate-template.xlsx
+++ b/src/assets/estimate-template.xlsx
@@ -8,17 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ICTMaintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7947033-901C-4A9C-A4BE-4E1B4841B74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC8CB1F-00FF-48AB-9FF3-E3E71820D1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="견적서" sheetId="1" r:id="rId1"/>
     <sheet name="세부내역" sheetId="2" r:id="rId2"/>
+    <sheet name="정보통신설비 기준인원 및 조정계수 기준" sheetId="4" r:id="rId3"/>
+    <sheet name="노임단가 기준" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">세부내역!$A$19:$H$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">견적서!$A$1:$H$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'노임단가 기준'!$A$1:$H$50</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">세부내역!$A$1:$H$26</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="149">
   <si>
     <t xml:space="preserve"> 발급일(Date)</t>
   </si>
@@ -374,6 +377,253 @@
   <si>
     <t>건</t>
     <phoneticPr fontId="22" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 통신설비</t>
+  </si>
+  <si>
+    <t>유지보수·관리 및 성능점검 대상 정보통신설비</t>
+  </si>
+  <si>
+    <t>단위</t>
+  </si>
+  <si>
+    <t>기준인원</t>
+  </si>
+  <si>
+    <t>(인)</t>
+  </si>
+  <si>
+    <t>조정계수 적용 여부</t>
+  </si>
+  <si>
+    <t>(연면적)</t>
+  </si>
+  <si>
+    <t>케이블설비</t>
+  </si>
+  <si>
+    <t>식</t>
+  </si>
+  <si>
+    <t>√</t>
+  </si>
+  <si>
+    <t>배관설비</t>
+  </si>
+  <si>
+    <t>국선인입설비</t>
+  </si>
+  <si>
+    <t>단자함설비</t>
+  </si>
+  <si>
+    <t>이동통신구내선로설비</t>
+  </si>
+  <si>
+    <t>전화설비</t>
+  </si>
+  <si>
+    <t>방송 공동수신 안테나 시설</t>
+  </si>
+  <si>
+    <t>종합유선방송 구내전송선로설비</t>
+  </si>
+  <si>
+    <t>2. 방송설비</t>
+  </si>
+  <si>
+    <t>방송음향설비</t>
+  </si>
+  <si>
+    <t>3. 정보설비</t>
+  </si>
+  <si>
+    <t>전자출입(통제)시스템</t>
+  </si>
+  <si>
+    <t>원격검침시스템</t>
+  </si>
+  <si>
+    <t>주차관제시스템</t>
+  </si>
+  <si>
+    <t>주차유도시스템</t>
+  </si>
+  <si>
+    <t>무인택배시스템</t>
+  </si>
+  <si>
+    <t>비상벨설비</t>
+  </si>
+  <si>
+    <t>영상정보처리기기 시스템</t>
+  </si>
+  <si>
+    <t>홈네트워크 설비(전유부분)</t>
+  </si>
+  <si>
+    <t>세대</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>빌딩안내시스템(BIS)</t>
+  </si>
+  <si>
+    <t>전기시계시스템</t>
+  </si>
+  <si>
+    <t>통합 SI시스템</t>
+  </si>
+  <si>
+    <t>시설관리시스템(Facility Management System)</t>
+  </si>
+  <si>
+    <t>건물에너지관리시스템(BEMS)</t>
+  </si>
+  <si>
+    <t>지능형 인원계수 시스템</t>
+  </si>
+  <si>
+    <t>지능형 경계 감시 시스템</t>
+  </si>
+  <si>
+    <t>스마트 병원 설비(의료용 너스콜)</t>
+  </si>
+  <si>
+    <t>스마트 도난방지 시스템</t>
+  </si>
+  <si>
+    <t>스마트 공장 시스템</t>
+  </si>
+  <si>
+    <t>스마트 도서관 시스템</t>
+  </si>
+  <si>
+    <t>개소</t>
+  </si>
+  <si>
+    <t>지능형 이상음원 시스템</t>
+  </si>
+  <si>
+    <t>IoT기반 지하공간 안전관리 시스템</t>
+  </si>
+  <si>
+    <t>디지털 사이니지</t>
+  </si>
+  <si>
+    <t>4. 기타설비</t>
+  </si>
+  <si>
+    <t>통신용 전원설비</t>
+  </si>
+  <si>
+    <t>통신접지설비</t>
+  </si>
+  <si>
+    <t>비고</t>
+  </si>
+  <si>
+    <t>1. 기준인원은 기술자 한 명이 유지보수·관리 또는 성능점검을 1회 실시하는데 투입되는 수량을 말한다.</t>
+  </si>
+  <si>
+    <t>2. 제8조제3항 및 제10조제3항에 따른 수리·교체 등에 소요되는 기술자의 투입 수량은 포함하지 않는다.</t>
+  </si>
+  <si>
+    <t>3. 단위의 “식” 등을 구분하여 적용한다.</t>
+  </si>
+  <si>
+    <t>4 “지능형 경계 감시 시스템”은 울타리, 철책, 담벼락 등 경계 구간의 거리 600m를 기준으로 하며, 거리별 증감에 따라 기준인원을 산정하여 적용한다.</t>
+  </si>
+  <si>
+    <t>연면적에 따른 조정계수</t>
+  </si>
+  <si>
+    <r>
+      <t>연면적</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="한양신명조"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>㎡</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>조정계수</t>
+  </si>
+  <si>
+    <t>5,000 이상 ~ 10,000 미만</t>
+  </si>
+  <si>
+    <t>10,000 이상 ~ 15,000 미만</t>
+  </si>
+  <si>
+    <t>15,000 이상 ~ 20,000 미만</t>
+  </si>
+  <si>
+    <t>20,000 이상 ~ 25,000 미만</t>
+  </si>
+  <si>
+    <t>25,000 이상 ~ 30,000 미만</t>
+  </si>
+  <si>
+    <t>30,000 이상 ~ 35,000 미만</t>
+  </si>
+  <si>
+    <t>35,000 이상 ~ 40,000 미만</t>
+  </si>
+  <si>
+    <t>40,000 이상 ~ 45,000 미만</t>
+  </si>
+  <si>
+    <t>45,000 이상 ~ 50,000 미만</t>
+  </si>
+  <si>
+    <t>50,000 이상 ~ 55,000 미만</t>
+  </si>
+  <si>
+    <t>55,000 이상 ~ 60,000 미만</t>
+  </si>
+  <si>
+    <t>60,000 이상</t>
+  </si>
+  <si>
+    <t>표 2 연면적에 따른 조정계수</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>표 1 유지보수·관리 및 성능점검 투입인원 산정 기준</t>
+    <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -393,7 +643,7 @@
     <numFmt numFmtId="183" formatCode="#,##0_);[Red]\(#,##0\)"/>
     <numFmt numFmtId="184" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -641,6 +891,36 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="한양신명조"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="한양신명조"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="한양신명조"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -680,7 +960,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1019,6 +1299,153 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1040,7 +1467,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1195,30 +1622,194 @@
     <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="5" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="5" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="5" borderId="22" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="18" fillId="5" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="24" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1238,9 +1829,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1252,178 +1840,95 @@
     <xf numFmtId="0" fontId="24" fillId="3" borderId="8" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="18" fillId="5" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="5" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="5" borderId="22" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="5" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1769,6 +2274,72 @@
         <a:xfrm>
           <a:off x="95250" y="57150"/>
           <a:ext cx="2028825" cy="366066"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="_x483631656">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{032F1DD7-01C4-8908-32A0-94A601EA1C1E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6096000" cy="8572500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2695,14 +3266,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.2" customHeight="1">
-      <c r="A1" s="99"/>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="101"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="98"/>
+      <c r="A1" s="68"/>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="67"/>
       <c r="I1" s="2"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -2711,16 +3282,16 @@
       <c r="N1" s="3"/>
     </row>
     <row r="2" spans="1:14" ht="43.5" customHeight="1">
-      <c r="A2" s="116" t="s">
+      <c r="A2" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="117"/>
-      <c r="C2" s="117"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="118"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="83"/>
       <c r="I2" s="2"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -2729,18 +3300,18 @@
       <c r="N2" s="3"/>
     </row>
     <row r="3" spans="1:14" ht="34.9" customHeight="1">
-      <c r="A3" s="106" t="s">
+      <c r="A3" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="107"/>
-      <c r="C3" s="107"/>
-      <c r="D3" s="109" t="s">
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="110"/>
-      <c r="F3" s="111"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="112"/>
+      <c r="E3" s="78"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="80"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -2748,14 +3319,14 @@
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:14" ht="34.9" customHeight="1">
-      <c r="A4" s="108"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="107"/>
-      <c r="D4" s="109"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="112"/>
+      <c r="A4" s="76"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="80"/>
       <c r="I4" s="4"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -2763,16 +3334,16 @@
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="34.9" customHeight="1">
-      <c r="A5" s="108"/>
-      <c r="B5" s="107"/>
-      <c r="C5" s="107"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="113" t="s">
+      <c r="A5" s="76"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="77"/>
+      <c r="E5" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="115"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="56"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
@@ -2780,20 +3351,20 @@
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A6" s="119" t="s">
+      <c r="A6" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102" t="s">
+      <c r="B6" s="53"/>
+      <c r="C6" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="102"/>
-      <c r="E6" s="120" t="s">
+      <c r="D6" s="53"/>
+      <c r="E6" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="113"/>
-      <c r="G6" s="113"/>
-      <c r="H6" s="121"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="57"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
@@ -2801,20 +3372,20 @@
       <c r="M6" s="5"/>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A7" s="119" t="s">
+      <c r="A7" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="102"/>
-      <c r="C7" s="102" t="s">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="102"/>
-      <c r="E7" s="113" t="s">
+      <c r="D7" s="53"/>
+      <c r="E7" s="54" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="114"/>
-      <c r="G7" s="114"/>
-      <c r="H7" s="115"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="56"/>
       <c r="I7"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -2822,20 +3393,20 @@
       <c r="M7" s="5"/>
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A8" s="119" t="s">
+      <c r="A8" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="102"/>
-      <c r="C8" s="103" t="s">
+      <c r="B8" s="53"/>
+      <c r="C8" s="71" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="103"/>
-      <c r="E8" s="113" t="s">
+      <c r="D8" s="71"/>
+      <c r="E8" s="54" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="113"/>
-      <c r="G8" s="113"/>
-      <c r="H8" s="121"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="57"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -2843,18 +3414,18 @@
       <c r="M8" s="5"/>
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A9" s="119" t="s">
+      <c r="A9" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="102"/>
-      <c r="C9" s="104" t="s">
+      <c r="B9" s="53"/>
+      <c r="C9" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="104"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="105"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="73"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -2862,19 +3433,19 @@
       <c r="M9" s="5"/>
     </row>
     <row r="10" spans="1:14" ht="39.6" customHeight="1">
-      <c r="A10" s="119" t="s">
+      <c r="A10" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="102"/>
-      <c r="C10" s="127">
+      <c r="B10" s="53"/>
+      <c r="C10" s="63">
         <f>ROUNDDOWN(G28,3)</f>
         <v>65511468</v>
       </c>
-      <c r="D10" s="128"/>
-      <c r="E10" s="128"/>
-      <c r="F10" s="128"/>
-      <c r="G10" s="128"/>
-      <c r="H10" s="129"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="65"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -2883,16 +3454,16 @@
       <c r="N10" s="3"/>
     </row>
     <row r="11" spans="1:14" ht="40.9" customHeight="1" thickBot="1">
-      <c r="A11" s="124" t="s">
+      <c r="A11" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="125"/>
-      <c r="C11" s="125"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="125"/>
-      <c r="G11" s="125"/>
-      <c r="H11" s="126"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="62"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -2901,10 +3472,10 @@
       <c r="N11" s="3"/>
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A12" s="122" t="s">
+      <c r="A12" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="123"/>
+      <c r="B12" s="59"/>
       <c r="C12" s="9" t="s">
         <v>9</v>
       </c>
@@ -2929,10 +3500,10 @@
       <c r="M12" s="5"/>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A13" s="79" t="s">
+      <c r="A13" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="80"/>
+      <c r="B13" s="94"/>
       <c r="C13" s="12">
         <v>29984.71</v>
       </c>
@@ -2956,10 +3527,10 @@
       <c r="M13" s="5"/>
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A14" s="79" t="s">
+      <c r="A14" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="80"/>
+      <c r="B14" s="94"/>
       <c r="C14" s="12">
         <v>29984.71</v>
       </c>
@@ -2983,10 +3554,10 @@
       <c r="M14" s="5"/>
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A15" s="79" t="s">
+      <c r="A15" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="80"/>
+      <c r="B15" s="94"/>
       <c r="C15" s="12">
         <v>29984.71</v>
       </c>
@@ -3010,16 +3581,16 @@
       <c r="M15" s="5"/>
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A16" s="81" t="s">
+      <c r="A16" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="82"/>
-      <c r="E16" s="82"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="82"/>
-      <c r="H16" s="83"/>
+      <c r="B16" s="96"/>
+      <c r="C16" s="96"/>
+      <c r="D16" s="96"/>
+      <c r="E16" s="96"/>
+      <c r="F16" s="96"/>
+      <c r="G16" s="96"/>
+      <c r="H16" s="97"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -3027,16 +3598,16 @@
       <c r="M16" s="5"/>
     </row>
     <row r="17" spans="1:13" s="1" customFormat="1" ht="8.4499999999999993" customHeight="1">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="85"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="86"/>
+      <c r="B17" s="99"/>
+      <c r="C17" s="99"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="100"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -3044,14 +3615,14 @@
       <c r="M17" s="5"/>
     </row>
     <row r="18" spans="1:13" s="1" customFormat="1" ht="6.6" customHeight="1">
-      <c r="A18" s="87"/>
-      <c r="B18" s="85"/>
-      <c r="C18" s="85"/>
-      <c r="D18" s="85"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="85"/>
-      <c r="H18" s="86"/>
+      <c r="A18" s="101"/>
+      <c r="B18" s="99"/>
+      <c r="C18" s="99"/>
+      <c r="D18" s="99"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="99"/>
+      <c r="H18" s="100"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
@@ -3059,14 +3630,14 @@
       <c r="M18" s="5"/>
     </row>
     <row r="19" spans="1:13" s="1" customFormat="1" ht="12" customHeight="1">
-      <c r="A19" s="87"/>
-      <c r="B19" s="85"/>
-      <c r="C19" s="85"/>
-      <c r="D19" s="85"/>
-      <c r="E19" s="85"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="86"/>
+      <c r="A19" s="101"/>
+      <c r="B19" s="99"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="99"/>
+      <c r="H19" s="100"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
@@ -3074,14 +3645,14 @@
       <c r="M19" s="5"/>
     </row>
     <row r="20" spans="1:13" s="1" customFormat="1" ht="53.25" customHeight="1">
-      <c r="A20" s="87"/>
-      <c r="B20" s="85"/>
-      <c r="C20" s="85"/>
-      <c r="D20" s="85"/>
-      <c r="E20" s="85"/>
-      <c r="F20" s="85"/>
-      <c r="G20" s="85"/>
-      <c r="H20" s="86"/>
+      <c r="A20" s="101"/>
+      <c r="B20" s="99"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="99"/>
+      <c r="H20" s="100"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
@@ -3089,14 +3660,14 @@
       <c r="M20" s="5"/>
     </row>
     <row r="21" spans="1:13" s="1" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A21" s="87"/>
-      <c r="B21" s="85"/>
-      <c r="C21" s="85"/>
-      <c r="D21" s="85"/>
-      <c r="E21" s="85"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="85"/>
-      <c r="H21" s="86"/>
+      <c r="A21" s="101"/>
+      <c r="B21" s="99"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="99"/>
+      <c r="H21" s="100"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
@@ -3104,14 +3675,14 @@
       <c r="M21" s="5"/>
     </row>
     <row r="22" spans="1:13" s="1" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A22" s="87"/>
-      <c r="B22" s="85"/>
-      <c r="C22" s="85"/>
-      <c r="D22" s="85"/>
-      <c r="E22" s="85"/>
-      <c r="F22" s="85"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="86"/>
+      <c r="A22" s="101"/>
+      <c r="B22" s="99"/>
+      <c r="C22" s="99"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="99"/>
+      <c r="G22" s="99"/>
+      <c r="H22" s="100"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
@@ -3119,14 +3690,14 @@
       <c r="M22" s="5"/>
     </row>
     <row r="23" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A23" s="87"/>
-      <c r="B23" s="85"/>
-      <c r="C23" s="85"/>
-      <c r="D23" s="85"/>
-      <c r="E23" s="85"/>
-      <c r="F23" s="85"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="86"/>
+      <c r="A23" s="101"/>
+      <c r="B23" s="99"/>
+      <c r="C23" s="99"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="99"/>
+      <c r="G23" s="99"/>
+      <c r="H23" s="100"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -3134,19 +3705,19 @@
       <c r="M23" s="5"/>
     </row>
     <row r="24" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A24" s="88" t="s">
+      <c r="A24" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="89"/>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="90">
+      <c r="B24" s="103"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="103"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="104">
         <f>SUM(G13:G15)</f>
         <v>59555880</v>
       </c>
-      <c r="H24" s="91"/>
+      <c r="H24" s="105"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
@@ -3154,18 +3725,18 @@
       <c r="M24" s="5"/>
     </row>
     <row r="25" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A25" s="92" t="s">
+      <c r="A25" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="93"/>
-      <c r="C25" s="93"/>
-      <c r="D25" s="93"/>
-      <c r="E25" s="93"/>
-      <c r="F25" s="94"/>
-      <c r="G25" s="95">
+      <c r="B25" s="107"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="107"/>
+      <c r="E25" s="107"/>
+      <c r="F25" s="108"/>
+      <c r="G25" s="109">
         <v>0</v>
       </c>
-      <c r="H25" s="96"/>
+      <c r="H25" s="110"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
@@ -3173,19 +3744,19 @@
       <c r="M25" s="5"/>
     </row>
     <row r="26" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A26" s="75" t="s">
+      <c r="A26" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="76"/>
-      <c r="C26" s="76"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="77">
+      <c r="B26" s="90"/>
+      <c r="C26" s="90"/>
+      <c r="D26" s="90"/>
+      <c r="E26" s="90"/>
+      <c r="F26" s="90"/>
+      <c r="G26" s="91">
         <f>G24-(G24*G25)</f>
         <v>59555880</v>
       </c>
-      <c r="H26" s="78"/>
+      <c r="H26" s="92"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
@@ -3193,19 +3764,19 @@
       <c r="M26" s="5"/>
     </row>
     <row r="27" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A27" s="88" t="s">
+      <c r="A27" s="102" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="89"/>
-      <c r="C27" s="89"/>
-      <c r="D27" s="89"/>
-      <c r="E27" s="89"/>
-      <c r="F27" s="89"/>
-      <c r="G27" s="90">
+      <c r="B27" s="103"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="103"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="103"/>
+      <c r="G27" s="104">
         <f>G26*10%</f>
         <v>5955588</v>
       </c>
-      <c r="H27" s="91"/>
+      <c r="H27" s="105"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
@@ -3213,19 +3784,19 @@
       <c r="M27" s="5"/>
     </row>
     <row r="28" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1" thickBot="1">
-      <c r="A28" s="71" t="s">
+      <c r="A28" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="72"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="72"/>
-      <c r="F28" s="72"/>
-      <c r="G28" s="73">
+      <c r="B28" s="86"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="86"/>
+      <c r="G28" s="87">
         <f>G26+G27</f>
         <v>65511468</v>
       </c>
-      <c r="H28" s="74"/>
+      <c r="H28" s="88"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
@@ -3235,13 +3806,21 @@
     <row r="29" spans="1:13" ht="408.75" customHeight="1" thickTop="1"/>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A17:H23"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="G25:H25"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C7:D7"/>
@@ -3257,21 +3836,13 @@
     <mergeCell ref="E6:H6"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A17:H23"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C10:H10"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3307,16 +3878,16 @@
     <row r="1" spans="1:10" ht="18.75" customHeight="1"/>
     <row r="2" spans="1:10" ht="18.75" customHeight="1"/>
     <row r="3" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="129" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
+      <c r="B3" s="129"/>
+      <c r="C3" s="129"/>
+      <c r="D3" s="129"/>
+      <c r="E3" s="129"/>
+      <c r="F3" s="129"/>
+      <c r="G3" s="129"/>
+      <c r="H3" s="129"/>
       <c r="I3" s="15"/>
       <c r="J3" s="15"/>
     </row>
@@ -3339,17 +3910,17 @@
       <c r="B5" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="115" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="52"/>
+      <c r="D5" s="115"/>
       <c r="E5" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="52" t="s">
+      <c r="F5" s="115" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="52"/>
+      <c r="G5" s="115"/>
       <c r="H5" s="34" t="s">
         <v>7</v>
       </c>
@@ -3361,17 +3932,17 @@
       <c r="B6" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="53">
+      <c r="C6" s="126">
         <v>29984.71</v>
       </c>
-      <c r="D6" s="54"/>
+      <c r="D6" s="127"/>
       <c r="E6" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="F6" s="55">
+      <c r="F6" s="128">
         <v>1.75</v>
       </c>
-      <c r="G6" s="55"/>
+      <c r="G6" s="128"/>
       <c r="H6" s="19"/>
     </row>
     <row r="7" spans="1:10" ht="20.25" customHeight="1">
@@ -3379,13 +3950,13 @@
       <c r="C7" s="14"/>
     </row>
     <row r="8" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="59"/>
+      <c r="B8" s="113"/>
+      <c r="C8" s="113"/>
+      <c r="D8" s="113"/>
+      <c r="E8" s="114"/>
       <c r="F8" s="35" t="s">
         <v>22</v>
       </c>
@@ -3400,12 +3971,12 @@
       <c r="A9" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="116" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="61"/>
-      <c r="D9" s="61"/>
-      <c r="E9" s="62"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="118"/>
       <c r="F9" s="21" t="s">
         <v>76</v>
       </c>
@@ -3415,15 +3986,15 @@
       <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A10" s="68" t="s">
+      <c r="A10" s="123" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="64" t="s">
+      <c r="B10" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="65"/>
-      <c r="E10" s="66"/>
+      <c r="C10" s="121"/>
+      <c r="D10" s="121"/>
+      <c r="E10" s="122"/>
       <c r="F10" s="21">
         <v>624275</v>
       </c>
@@ -3431,13 +4002,13 @@
       <c r="H10" s="23"/>
     </row>
     <row r="11" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A11" s="69"/>
-      <c r="B11" s="64" t="s">
+      <c r="A11" s="124"/>
+      <c r="B11" s="120" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="66"/>
+      <c r="C11" s="121"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="122"/>
       <c r="F11" s="21">
         <v>0</v>
       </c>
@@ -3445,13 +4016,13 @@
       <c r="H11" s="44"/>
     </row>
     <row r="12" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A12" s="70"/>
-      <c r="B12" s="64" t="s">
+      <c r="A12" s="125"/>
+      <c r="B12" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="65"/>
-      <c r="D12" s="65"/>
-      <c r="E12" s="66"/>
+      <c r="C12" s="121"/>
+      <c r="D12" s="121"/>
+      <c r="E12" s="122"/>
       <c r="F12" s="21">
         <v>0</v>
       </c>
@@ -3459,13 +4030,13 @@
       <c r="H12" s="44"/>
     </row>
     <row r="13" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="115" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="52"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
+      <c r="B13" s="115"/>
+      <c r="C13" s="115"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="115"/>
       <c r="F13" s="37">
         <f>SUM(F9:F12)</f>
         <v>624275</v>
@@ -3510,13 +4081,13 @@
       <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A16" s="52" t="s">
+      <c r="A16" s="115" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="52"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
+      <c r="B16" s="115"/>
+      <c r="C16" s="115"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="115"/>
       <c r="F16" s="40">
         <v>12984929.666800003</v>
       </c>
@@ -3524,13 +4095,13 @@
       <c r="H16" s="41"/>
     </row>
     <row r="17" spans="1:8" ht="27" customHeight="1">
-      <c r="A17" s="67" t="s">
+      <c r="A17" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="67"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="67"/>
-      <c r="E17" s="67"/>
+      <c r="B17" s="111"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="111"/>
       <c r="F17" s="24">
         <v>19851959.779050007</v>
       </c>
@@ -3552,12 +4123,12 @@
       <c r="A20" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="59"/>
+      <c r="C20" s="113"/>
+      <c r="D20" s="113"/>
+      <c r="E20" s="114"/>
       <c r="F20" s="34" t="s">
         <v>36</v>
       </c>
@@ -3572,12 +4143,12 @@
       <c r="A21" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="63" t="s">
+      <c r="B21" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="63"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="63"/>
+      <c r="C21" s="119"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="119"/>
       <c r="F21" s="46" t="s">
         <v>27</v>
       </c>
@@ -3588,12 +4159,12 @@
       <c r="A22" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="63" t="s">
+      <c r="B22" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
+      <c r="C22" s="119"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
       <c r="F22" s="46" t="s">
         <v>27</v>
       </c>
@@ -3604,12 +4175,12 @@
       <c r="A23" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="119" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
+      <c r="C23" s="119"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
       <c r="F23" s="46" t="s">
         <v>27</v>
       </c>
@@ -3620,12 +4191,12 @@
       <c r="A24" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="63" t="s">
+      <c r="B24" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
+      <c r="C24" s="119"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
       <c r="F24" s="46" t="s">
         <v>27</v>
       </c>
@@ -3636,13 +4207,13 @@
       <c r="A25" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="67" t="s">
+      <c r="B25" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="67"/>
+      <c r="C25" s="111"/>
+      <c r="D25" s="111"/>
+      <c r="E25" s="111"/>
+      <c r="F25" s="111"/>
       <c r="G25" s="49">
         <f>SUM(G21:G24)</f>
         <v>0</v>
@@ -3657,11 +4228,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A3:H3"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B24:E24"/>
@@ -3672,11 +4243,11 @@
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="H21:H24">
@@ -3688,4 +4259,820 @@
   <pageSetup paperSize="9" scale="79" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BD8BB87-EF45-4335-B0BA-17C6A12C5B68}">
+  <dimension ref="A1:H55"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="46.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="14.25">
+      <c r="A1" s="155" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="G1" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="H1" s="154"/>
+    </row>
+    <row r="2" spans="1:8" ht="14.25">
+      <c r="A2" s="134" t="s">
+        <v>79</v>
+      </c>
+      <c r="B2" s="134"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="134"/>
+      <c r="G2" s="152" t="s">
+        <v>132</v>
+      </c>
+      <c r="H2" s="153"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="135" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="135" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="130" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3" s="151" t="s">
+        <v>133</v>
+      </c>
+      <c r="H3" s="151" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="136"/>
+      <c r="B4" s="136"/>
+      <c r="C4" s="131" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="131" t="s">
+        <v>85</v>
+      </c>
+      <c r="G4" s="132" t="s">
+        <v>135</v>
+      </c>
+      <c r="H4" s="132">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="132" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="132" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="132">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="D5" s="132" t="s">
+        <v>88</v>
+      </c>
+      <c r="G5" s="132" t="s">
+        <v>136</v>
+      </c>
+      <c r="H5" s="132">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="133" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="133">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="D6" s="133" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="132" t="s">
+        <v>137</v>
+      </c>
+      <c r="H6" s="132">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="133" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="133">
+        <v>0.17</v>
+      </c>
+      <c r="D7" s="133" t="s">
+        <v>88</v>
+      </c>
+      <c r="G7" s="132" t="s">
+        <v>138</v>
+      </c>
+      <c r="H7" s="132">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="133" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="133">
+        <v>0.24</v>
+      </c>
+      <c r="D8" s="133" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="132" t="s">
+        <v>139</v>
+      </c>
+      <c r="H8" s="132">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="133" t="s">
+        <v>92</v>
+      </c>
+      <c r="B9" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="133">
+        <v>0.06</v>
+      </c>
+      <c r="D9" s="133" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="132" t="s">
+        <v>140</v>
+      </c>
+      <c r="H9" s="132">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="133" t="s">
+        <v>93</v>
+      </c>
+      <c r="B10" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="133">
+        <v>0.1</v>
+      </c>
+      <c r="D10" s="133" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="132" t="s">
+        <v>141</v>
+      </c>
+      <c r="H10" s="132">
+        <v>2.0499999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="132" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="132" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="132">
+        <v>0.89</v>
+      </c>
+      <c r="D11" s="132" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" s="132" t="s">
+        <v>142</v>
+      </c>
+      <c r="H11" s="132">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="132" t="s">
+        <v>95</v>
+      </c>
+      <c r="B12" s="132" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="132">
+        <v>0.52</v>
+      </c>
+      <c r="D12" s="132" t="s">
+        <v>88</v>
+      </c>
+      <c r="G12" s="132" t="s">
+        <v>143</v>
+      </c>
+      <c r="H12" s="132">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="137"/>
+      <c r="B13" s="137"/>
+      <c r="C13" s="137"/>
+      <c r="D13" s="137"/>
+      <c r="G13" s="132" t="s">
+        <v>144</v>
+      </c>
+      <c r="H13" s="132">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14.25">
+      <c r="A14" s="134" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="134"/>
+      <c r="C14" s="134"/>
+      <c r="D14" s="134"/>
+      <c r="G14" s="132" t="s">
+        <v>145</v>
+      </c>
+      <c r="H14" s="132">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="135" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" s="135" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="130" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="132" t="s">
+        <v>146</v>
+      </c>
+      <c r="H15" s="132">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="136"/>
+      <c r="B16" s="136"/>
+      <c r="C16" s="131" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="131" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="132" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="132" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="132">
+        <v>0.5</v>
+      </c>
+      <c r="D17" s="132" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="137"/>
+      <c r="B18" s="137"/>
+      <c r="C18" s="137"/>
+      <c r="D18" s="137"/>
+    </row>
+    <row r="19" spans="1:4" ht="14.25">
+      <c r="A19" s="134" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="134"/>
+      <c r="C19" s="134"/>
+      <c r="D19" s="134"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="135" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="135" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="130" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="136"/>
+      <c r="B21" s="136"/>
+      <c r="C21" s="131" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="131" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="133" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="133">
+        <v>1.85</v>
+      </c>
+      <c r="D22" s="133" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="133" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="133">
+        <v>0.83</v>
+      </c>
+      <c r="D23" s="133" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="133" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" s="133">
+        <v>0.52</v>
+      </c>
+      <c r="D24" s="133" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="133" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="133">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="D25" s="133" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="133" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="133">
+        <v>0.66</v>
+      </c>
+      <c r="D26" s="133" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="133" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="133">
+        <v>0.77</v>
+      </c>
+      <c r="D27" s="133" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="133" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="133">
+        <v>0.44</v>
+      </c>
+      <c r="D28" s="133" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="133" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="133">
+        <v>0.81</v>
+      </c>
+      <c r="D29" s="133" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="132" t="s">
+        <v>106</v>
+      </c>
+      <c r="B30" s="132" t="s">
+        <v>107</v>
+      </c>
+      <c r="C30" s="132">
+        <v>0.03</v>
+      </c>
+      <c r="D30" s="132" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="133" t="s">
+        <v>109</v>
+      </c>
+      <c r="B31" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="133">
+        <v>1.69</v>
+      </c>
+      <c r="D31" s="133" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="133" t="s">
+        <v>110</v>
+      </c>
+      <c r="B32" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="133">
+        <v>0.46</v>
+      </c>
+      <c r="D32" s="133" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="133" t="s">
+        <v>111</v>
+      </c>
+      <c r="B33" s="133" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="133">
+        <v>0.46</v>
+      </c>
+      <c r="D33" s="133" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="132" t="s">
+        <v>112</v>
+      </c>
+      <c r="B34" s="132" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34" s="132">
+        <v>0.54</v>
+      </c>
+      <c r="D34" s="132" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="132" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" s="132" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="132">
+        <v>0.76</v>
+      </c>
+      <c r="D35" s="132" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="132" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" s="132" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="132">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="D36" s="132" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="132" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" s="132" t="s">
+        <v>87</v>
+      </c>
+      <c r="C37" s="132">
+        <v>0.8</v>
+      </c>
+      <c r="D37" s="132" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="132" t="s">
+        <v>116</v>
+      </c>
+      <c r="B38" s="132" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="132">
+        <v>2.12</v>
+      </c>
+      <c r="D38" s="132" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="132" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" s="132" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="132">
+        <v>0.17</v>
+      </c>
+      <c r="D39" s="132" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="132" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="132" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="132">
+        <v>0.31</v>
+      </c>
+      <c r="D40" s="132" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="132" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" s="132" t="s">
+        <v>120</v>
+      </c>
+      <c r="C41" s="132">
+        <v>0.52</v>
+      </c>
+      <c r="D41" s="132" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="132" t="s">
+        <v>121</v>
+      </c>
+      <c r="B42" s="132" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" s="132">
+        <v>0.64</v>
+      </c>
+      <c r="D42" s="132" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="132" t="s">
+        <v>122</v>
+      </c>
+      <c r="B43" s="132" t="s">
+        <v>120</v>
+      </c>
+      <c r="C43" s="132">
+        <v>0.13</v>
+      </c>
+      <c r="D43" s="132" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="132" t="s">
+        <v>123</v>
+      </c>
+      <c r="B44" s="132" t="s">
+        <v>120</v>
+      </c>
+      <c r="C44" s="132">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="D44" s="132" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="138"/>
+      <c r="B45" s="137"/>
+      <c r="C45" s="137"/>
+      <c r="D45" s="139"/>
+    </row>
+    <row r="46" spans="1:4" ht="14.25">
+      <c r="A46" s="140" t="s">
+        <v>124</v>
+      </c>
+      <c r="B46" s="134"/>
+      <c r="C46" s="134"/>
+      <c r="D46" s="141"/>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="135" t="s">
+        <v>80</v>
+      </c>
+      <c r="B47" s="135" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" s="130" t="s">
+        <v>82</v>
+      </c>
+      <c r="D47" s="130" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="136"/>
+      <c r="B48" s="136"/>
+      <c r="C48" s="131" t="s">
+        <v>83</v>
+      </c>
+      <c r="D48" s="131" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="132" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49" s="132" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="132">
+        <v>1.66</v>
+      </c>
+      <c r="D49" s="132" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="132" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" s="132" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" s="132">
+        <v>0.12</v>
+      </c>
+      <c r="D50" s="132" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="142" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" s="143"/>
+      <c r="C51" s="143"/>
+      <c r="D51" s="144"/>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="145" t="s">
+        <v>128</v>
+      </c>
+      <c r="B52" s="146"/>
+      <c r="C52" s="146"/>
+      <c r="D52" s="147"/>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="145" t="s">
+        <v>129</v>
+      </c>
+      <c r="B53" s="146"/>
+      <c r="C53" s="146"/>
+      <c r="D53" s="147"/>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="145" t="s">
+        <v>130</v>
+      </c>
+      <c r="B54" s="146"/>
+      <c r="C54" s="146"/>
+      <c r="D54" s="147"/>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="148" t="s">
+        <v>131</v>
+      </c>
+      <c r="B55" s="149"/>
+      <c r="C55" s="149"/>
+      <c r="D55" s="150"/>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <phoneticPr fontId="14" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9D56256-763D-45FE-8A88-85EEC7B05681}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData/>
+  <phoneticPr fontId="14" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/src/assets/estimate-template.xlsx
+++ b/src/assets/estimate-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ICTMaintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC8CB1F-00FF-48AB-9FF3-E3E71820D1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C667DED-CC80-441E-B047-5E3F28F30632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1622,10 +1622,145 @@
     <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="5" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="5" borderId="22" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1637,6 +1772,17 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1664,138 +1810,19 @@
     <xf numFmtId="5" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="15" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="5" borderId="21" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="5" borderId="22" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="5" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="18" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1805,9 +1832,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1840,17 +1864,29 @@
     <xf numFmtId="0" fontId="24" fillId="3" borderId="8" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="18" fillId="5" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="18" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1858,20 +1894,20 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -1882,50 +1918,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3266,14 +3266,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.2" customHeight="1">
-      <c r="A1" s="68"/>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="67"/>
+      <c r="A1" s="85"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="84"/>
       <c r="I1" s="2"/>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
@@ -3282,16 +3282,16 @@
       <c r="N1" s="3"/>
     </row>
     <row r="2" spans="1:14" ht="43.5" customHeight="1">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="102" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="83"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="104"/>
       <c r="I2" s="2"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
@@ -3300,18 +3300,18 @@
       <c r="N2" s="3"/>
     </row>
     <row r="3" spans="1:14" ht="34.9" customHeight="1">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="77" t="s">
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="E3" s="78"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="80"/>
+      <c r="E3" s="96"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="98"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -3319,14 +3319,14 @@
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:14" ht="34.9" customHeight="1">
-      <c r="A4" s="76"/>
-      <c r="B4" s="75"/>
-      <c r="C4" s="75"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="80"/>
+      <c r="A4" s="94"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="98"/>
       <c r="I4" s="4"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -3334,16 +3334,16 @@
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="34.9" customHeight="1">
-      <c r="A5" s="76"/>
-      <c r="B5" s="75"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="54" t="s">
+      <c r="A5" s="94"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="56"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="101"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
@@ -3351,20 +3351,20 @@
       <c r="M5" s="5"/>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="53"/>
-      <c r="C6" s="53" t="s">
+      <c r="B6" s="88"/>
+      <c r="C6" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="53"/>
-      <c r="E6" s="84" t="s">
+      <c r="D6" s="88"/>
+      <c r="E6" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="57"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="107"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
@@ -3372,20 +3372,20 @@
       <c r="M6" s="5"/>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53" t="s">
+      <c r="B7" s="88"/>
+      <c r="C7" s="88" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="53"/>
-      <c r="E7" s="54" t="s">
+      <c r="D7" s="88"/>
+      <c r="E7" s="99" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="56"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="101"/>
       <c r="I7"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -3393,20 +3393,20 @@
       <c r="M7" s="5"/>
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="71" t="s">
+      <c r="B8" s="88"/>
+      <c r="C8" s="89" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="71"/>
-      <c r="E8" s="54" t="s">
+      <c r="D8" s="89"/>
+      <c r="E8" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="57"/>
+      <c r="F8" s="99"/>
+      <c r="G8" s="99"/>
+      <c r="H8" s="107"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -3414,18 +3414,18 @@
       <c r="M8" s="5"/>
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="39.6" customHeight="1">
-      <c r="A9" s="52" t="s">
+      <c r="A9" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="53"/>
-      <c r="C9" s="72" t="s">
+      <c r="B9" s="88"/>
+      <c r="C9" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="73"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="90"/>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="91"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -3433,19 +3433,19 @@
       <c r="M9" s="5"/>
     </row>
     <row r="10" spans="1:14" ht="39.6" customHeight="1">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="63">
+      <c r="B10" s="88"/>
+      <c r="C10" s="113">
         <f>ROUNDDOWN(G28,3)</f>
-        <v>65511468</v>
-      </c>
-      <c r="D10" s="64"/>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="65"/>
+        <v>65511000</v>
+      </c>
+      <c r="D10" s="114"/>
+      <c r="E10" s="114"/>
+      <c r="F10" s="114"/>
+      <c r="G10" s="114"/>
+      <c r="H10" s="115"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -3454,16 +3454,16 @@
       <c r="N10" s="3"/>
     </row>
     <row r="11" spans="1:14" ht="40.9" customHeight="1" thickBot="1">
-      <c r="A11" s="60" t="s">
+      <c r="A11" s="110" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="61"/>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="62"/>
+      <c r="B11" s="111"/>
+      <c r="C11" s="111"/>
+      <c r="D11" s="111"/>
+      <c r="E11" s="111"/>
+      <c r="F11" s="111"/>
+      <c r="G11" s="111"/>
+      <c r="H11" s="112"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -3472,10 +3472,10 @@
       <c r="N11" s="3"/>
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A12" s="58" t="s">
+      <c r="A12" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="59"/>
+      <c r="B12" s="109"/>
       <c r="C12" s="9" t="s">
         <v>9</v>
       </c>
@@ -3500,10 +3500,10 @@
       <c r="M12" s="5"/>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A13" s="93" t="s">
+      <c r="A13" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="94"/>
+      <c r="B13" s="66"/>
       <c r="C13" s="12">
         <v>29984.71</v>
       </c>
@@ -3527,10 +3527,10 @@
       <c r="M13" s="5"/>
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A14" s="93" t="s">
+      <c r="A14" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="94"/>
+      <c r="B14" s="66"/>
       <c r="C14" s="12">
         <v>29984.71</v>
       </c>
@@ -3554,10 +3554,10 @@
       <c r="M14" s="5"/>
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="40.5" customHeight="1">
-      <c r="A15" s="93" t="s">
+      <c r="A15" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="94"/>
+      <c r="B15" s="66"/>
       <c r="C15" s="12">
         <v>29984.71</v>
       </c>
@@ -3581,16 +3581,16 @@
       <c r="M15" s="5"/>
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="30" customHeight="1">
-      <c r="A16" s="95" t="s">
+      <c r="A16" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="96"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="96"/>
-      <c r="E16" s="96"/>
-      <c r="F16" s="96"/>
-      <c r="G16" s="96"/>
-      <c r="H16" s="97"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="68"/>
+      <c r="G16" s="68"/>
+      <c r="H16" s="69"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -3598,16 +3598,16 @@
       <c r="M16" s="5"/>
     </row>
     <row r="17" spans="1:13" s="1" customFormat="1" ht="8.4499999999999993" customHeight="1">
-      <c r="A17" s="98" t="s">
+      <c r="A17" s="70" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="99"/>
-      <c r="C17" s="99"/>
-      <c r="D17" s="99"/>
-      <c r="E17" s="99"/>
-      <c r="F17" s="99"/>
-      <c r="G17" s="99"/>
-      <c r="H17" s="100"/>
+      <c r="B17" s="71"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="72"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -3615,14 +3615,14 @@
       <c r="M17" s="5"/>
     </row>
     <row r="18" spans="1:13" s="1" customFormat="1" ht="6.6" customHeight="1">
-      <c r="A18" s="101"/>
-      <c r="B18" s="99"/>
-      <c r="C18" s="99"/>
-      <c r="D18" s="99"/>
-      <c r="E18" s="99"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="99"/>
-      <c r="H18" s="100"/>
+      <c r="A18" s="73"/>
+      <c r="B18" s="71"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="72"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
@@ -3630,14 +3630,14 @@
       <c r="M18" s="5"/>
     </row>
     <row r="19" spans="1:13" s="1" customFormat="1" ht="12" customHeight="1">
-      <c r="A19" s="101"/>
-      <c r="B19" s="99"/>
-      <c r="C19" s="99"/>
-      <c r="D19" s="99"/>
-      <c r="E19" s="99"/>
-      <c r="F19" s="99"/>
-      <c r="G19" s="99"/>
-      <c r="H19" s="100"/>
+      <c r="A19" s="73"/>
+      <c r="B19" s="71"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="72"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
@@ -3645,14 +3645,14 @@
       <c r="M19" s="5"/>
     </row>
     <row r="20" spans="1:13" s="1" customFormat="1" ht="53.25" customHeight="1">
-      <c r="A20" s="101"/>
-      <c r="B20" s="99"/>
-      <c r="C20" s="99"/>
-      <c r="D20" s="99"/>
-      <c r="E20" s="99"/>
-      <c r="F20" s="99"/>
-      <c r="G20" s="99"/>
-      <c r="H20" s="100"/>
+      <c r="A20" s="73"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="72"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
@@ -3660,14 +3660,14 @@
       <c r="M20" s="5"/>
     </row>
     <row r="21" spans="1:13" s="1" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A21" s="101"/>
-      <c r="B21" s="99"/>
-      <c r="C21" s="99"/>
-      <c r="D21" s="99"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="99"/>
-      <c r="G21" s="99"/>
-      <c r="H21" s="100"/>
+      <c r="A21" s="73"/>
+      <c r="B21" s="71"/>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="72"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
@@ -3675,14 +3675,14 @@
       <c r="M21" s="5"/>
     </row>
     <row r="22" spans="1:13" s="1" customFormat="1" ht="30.75" customHeight="1">
-      <c r="A22" s="101"/>
-      <c r="B22" s="99"/>
-      <c r="C22" s="99"/>
-      <c r="D22" s="99"/>
-      <c r="E22" s="99"/>
-      <c r="F22" s="99"/>
-      <c r="G22" s="99"/>
-      <c r="H22" s="100"/>
+      <c r="A22" s="73"/>
+      <c r="B22" s="71"/>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="72"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
@@ -3690,14 +3690,14 @@
       <c r="M22" s="5"/>
     </row>
     <row r="23" spans="1:13" s="1" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A23" s="101"/>
-      <c r="B23" s="99"/>
-      <c r="C23" s="99"/>
-      <c r="D23" s="99"/>
-      <c r="E23" s="99"/>
-      <c r="F23" s="99"/>
-      <c r="G23" s="99"/>
-      <c r="H23" s="100"/>
+      <c r="A23" s="73"/>
+      <c r="B23" s="71"/>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="71"/>
+      <c r="F23" s="71"/>
+      <c r="G23" s="71"/>
+      <c r="H23" s="72"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -3705,19 +3705,19 @@
       <c r="M23" s="5"/>
     </row>
     <row r="24" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A24" s="102" t="s">
+      <c r="A24" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="103"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="103"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="103"/>
-      <c r="G24" s="104">
+      <c r="B24" s="75"/>
+      <c r="C24" s="75"/>
+      <c r="D24" s="75"/>
+      <c r="E24" s="75"/>
+      <c r="F24" s="75"/>
+      <c r="G24" s="76">
         <f>SUM(G13:G15)</f>
         <v>59555880</v>
       </c>
-      <c r="H24" s="105"/>
+      <c r="H24" s="77"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
@@ -3725,18 +3725,18 @@
       <c r="M24" s="5"/>
     </row>
     <row r="25" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A25" s="106" t="s">
+      <c r="A25" s="78" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="107"/>
-      <c r="C25" s="107"/>
-      <c r="D25" s="107"/>
-      <c r="E25" s="107"/>
-      <c r="F25" s="108"/>
-      <c r="G25" s="109">
+      <c r="B25" s="79"/>
+      <c r="C25" s="79"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="79"/>
+      <c r="F25" s="80"/>
+      <c r="G25" s="81">
         <v>0</v>
       </c>
-      <c r="H25" s="110"/>
+      <c r="H25" s="82"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
@@ -3744,19 +3744,19 @@
       <c r="M25" s="5"/>
     </row>
     <row r="26" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A26" s="89" t="s">
+      <c r="A26" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="B26" s="90"/>
-      <c r="C26" s="90"/>
-      <c r="D26" s="90"/>
-      <c r="E26" s="90"/>
-      <c r="F26" s="90"/>
-      <c r="G26" s="91">
+      <c r="B26" s="62"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="63">
         <f>G24-(G24*G25)</f>
         <v>59555880</v>
       </c>
-      <c r="H26" s="92"/>
+      <c r="H26" s="64"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
@@ -3764,19 +3764,19 @@
       <c r="M26" s="5"/>
     </row>
     <row r="27" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A27" s="102" t="s">
+      <c r="A27" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="103"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="103"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="103"/>
-      <c r="G27" s="104">
+      <c r="B27" s="75"/>
+      <c r="C27" s="75"/>
+      <c r="D27" s="75"/>
+      <c r="E27" s="75"/>
+      <c r="F27" s="75"/>
+      <c r="G27" s="76">
         <f>G26*10%</f>
         <v>5955588</v>
       </c>
-      <c r="H27" s="105"/>
+      <c r="H27" s="77"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
@@ -3784,19 +3784,19 @@
       <c r="M27" s="5"/>
     </row>
     <row r="28" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1" thickBot="1">
-      <c r="A28" s="85" t="s">
+      <c r="A28" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="86"/>
-      <c r="C28" s="86"/>
-      <c r="D28" s="86"/>
-      <c r="E28" s="86"/>
-      <c r="F28" s="86"/>
-      <c r="G28" s="87">
-        <f>G26+G27</f>
-        <v>65511468</v>
-      </c>
-      <c r="H28" s="88"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="59">
+        <f>ROUNDDOWN(G26+G27,-3)</f>
+        <v>65511000</v>
+      </c>
+      <c r="H28" s="60"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
@@ -3806,6 +3806,28 @@
     <row r="29" spans="1:13" ht="408.75" customHeight="1" thickTop="1"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="A3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:H4"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="A28:F28"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="A26:F26"/>
@@ -3821,28 +3843,6 @@
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="A3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:H4"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C10:H10"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3878,16 +3878,16 @@
     <row r="1" spans="1:10" ht="18.75" customHeight="1"/>
     <row r="2" spans="1:10" ht="18.75" customHeight="1"/>
     <row r="3" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A3" s="129" t="s">
+      <c r="A3" s="120" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="129"/>
-      <c r="C3" s="129"/>
-      <c r="D3" s="129"/>
-      <c r="E3" s="129"/>
-      <c r="F3" s="129"/>
-      <c r="G3" s="129"/>
-      <c r="H3" s="129"/>
+      <c r="B3" s="120"/>
+      <c r="C3" s="120"/>
+      <c r="D3" s="120"/>
+      <c r="E3" s="120"/>
+      <c r="F3" s="120"/>
+      <c r="G3" s="120"/>
+      <c r="H3" s="120"/>
       <c r="I3" s="15"/>
       <c r="J3" s="15"/>
     </row>
@@ -3910,17 +3910,17 @@
       <c r="B5" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="115" t="s">
+      <c r="C5" s="116" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="115"/>
+      <c r="D5" s="116"/>
       <c r="E5" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="115" t="s">
+      <c r="F5" s="116" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="115"/>
+      <c r="G5" s="116"/>
       <c r="H5" s="34" t="s">
         <v>7</v>
       </c>
@@ -3932,17 +3932,17 @@
       <c r="B6" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="126">
+      <c r="C6" s="117">
         <v>29984.71</v>
       </c>
-      <c r="D6" s="127"/>
+      <c r="D6" s="118"/>
       <c r="E6" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="F6" s="128">
+      <c r="F6" s="119">
         <v>1.75</v>
       </c>
-      <c r="G6" s="128"/>
+      <c r="G6" s="119"/>
       <c r="H6" s="19"/>
     </row>
     <row r="7" spans="1:10" ht="20.25" customHeight="1">
@@ -3950,13 +3950,13 @@
       <c r="C7" s="14"/>
     </row>
     <row r="8" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A8" s="112" t="s">
+      <c r="A8" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="113"/>
-      <c r="C8" s="113"/>
-      <c r="D8" s="113"/>
-      <c r="E8" s="114"/>
+      <c r="B8" s="122"/>
+      <c r="C8" s="122"/>
+      <c r="D8" s="122"/>
+      <c r="E8" s="123"/>
       <c r="F8" s="35" t="s">
         <v>22</v>
       </c>
@@ -3971,12 +3971,12 @@
       <c r="A9" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="116" t="s">
+      <c r="B9" s="124" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="118"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="126"/>
       <c r="F9" s="21" t="s">
         <v>76</v>
       </c>
@@ -3986,15 +3986,15 @@
       <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A10" s="123" t="s">
+      <c r="A10" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="120" t="s">
+      <c r="B10" s="128" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="122"/>
+      <c r="C10" s="129"/>
+      <c r="D10" s="129"/>
+      <c r="E10" s="130"/>
       <c r="F10" s="21">
         <v>624275</v>
       </c>
@@ -4002,13 +4002,13 @@
       <c r="H10" s="23"/>
     </row>
     <row r="11" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A11" s="124"/>
-      <c r="B11" s="120" t="s">
+      <c r="A11" s="132"/>
+      <c r="B11" s="128" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="121"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="122"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="130"/>
       <c r="F11" s="21">
         <v>0</v>
       </c>
@@ -4016,13 +4016,13 @@
       <c r="H11" s="44"/>
     </row>
     <row r="12" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A12" s="125"/>
-      <c r="B12" s="120" t="s">
+      <c r="A12" s="133"/>
+      <c r="B12" s="128" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="121"/>
-      <c r="D12" s="121"/>
-      <c r="E12" s="122"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="129"/>
+      <c r="E12" s="130"/>
       <c r="F12" s="21">
         <v>0</v>
       </c>
@@ -4030,13 +4030,13 @@
       <c r="H12" s="44"/>
     </row>
     <row r="13" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A13" s="115" t="s">
+      <c r="A13" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="115"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="115"/>
-      <c r="E13" s="115"/>
+      <c r="B13" s="116"/>
+      <c r="C13" s="116"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="116"/>
       <c r="F13" s="37">
         <f>SUM(F9:F12)</f>
         <v>624275</v>
@@ -4081,13 +4081,13 @@
       <c r="H15" s="29"/>
     </row>
     <row r="16" spans="1:10" ht="20.25" customHeight="1">
-      <c r="A16" s="115" t="s">
+      <c r="A16" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="115"/>
-      <c r="C16" s="115"/>
-      <c r="D16" s="115"/>
-      <c r="E16" s="115"/>
+      <c r="B16" s="116"/>
+      <c r="C16" s="116"/>
+      <c r="D16" s="116"/>
+      <c r="E16" s="116"/>
       <c r="F16" s="40">
         <v>12984929.666800003</v>
       </c>
@@ -4095,13 +4095,13 @@
       <c r="H16" s="41"/>
     </row>
     <row r="17" spans="1:8" ht="27" customHeight="1">
-      <c r="A17" s="111" t="s">
+      <c r="A17" s="134" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="111"/>
-      <c r="C17" s="111"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="111"/>
+      <c r="B17" s="134"/>
+      <c r="C17" s="134"/>
+      <c r="D17" s="134"/>
+      <c r="E17" s="134"/>
       <c r="F17" s="24">
         <v>19851959.779050007</v>
       </c>
@@ -4123,12 +4123,12 @@
       <c r="A20" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="112" t="s">
+      <c r="B20" s="121" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="113"/>
-      <c r="D20" s="113"/>
-      <c r="E20" s="114"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="122"/>
+      <c r="E20" s="123"/>
       <c r="F20" s="34" t="s">
         <v>36</v>
       </c>
@@ -4143,12 +4143,12 @@
       <c r="A21" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="119" t="s">
+      <c r="B21" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="119"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="119"/>
+      <c r="C21" s="127"/>
+      <c r="D21" s="127"/>
+      <c r="E21" s="127"/>
       <c r="F21" s="46" t="s">
         <v>27</v>
       </c>
@@ -4159,12 +4159,12 @@
       <c r="A22" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="119"/>
-      <c r="D22" s="119"/>
-      <c r="E22" s="119"/>
+      <c r="C22" s="127"/>
+      <c r="D22" s="127"/>
+      <c r="E22" s="127"/>
       <c r="F22" s="46" t="s">
         <v>27</v>
       </c>
@@ -4175,12 +4175,12 @@
       <c r="A23" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="119" t="s">
+      <c r="B23" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="119"/>
-      <c r="D23" s="119"/>
-      <c r="E23" s="119"/>
+      <c r="C23" s="127"/>
+      <c r="D23" s="127"/>
+      <c r="E23" s="127"/>
       <c r="F23" s="46" t="s">
         <v>27</v>
       </c>
@@ -4191,12 +4191,12 @@
       <c r="A24" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="119" t="s">
+      <c r="B24" s="127" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="119"/>
-      <c r="D24" s="119"/>
-      <c r="E24" s="119"/>
+      <c r="C24" s="127"/>
+      <c r="D24" s="127"/>
+      <c r="E24" s="127"/>
       <c r="F24" s="46" t="s">
         <v>27</v>
       </c>
@@ -4207,13 +4207,13 @@
       <c r="A25" s="50" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="111" t="s">
+      <c r="B25" s="134" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="111"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="111"/>
+      <c r="C25" s="134"/>
+      <c r="D25" s="134"/>
+      <c r="E25" s="134"/>
+      <c r="F25" s="134"/>
       <c r="G25" s="49">
         <f>SUM(G21:G24)</f>
         <v>0</v>
@@ -4228,11 +4228,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A17:E17"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B24:E24"/>
@@ -4243,11 +4243,11 @@
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A3:H3"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="H21:H24">
@@ -4281,757 +4281,764 @@
       <c r="B1" s="155"/>
       <c r="C1" s="155"/>
       <c r="D1" s="155"/>
-      <c r="G1" s="154" t="s">
+      <c r="G1" s="152" t="s">
         <v>147</v>
       </c>
-      <c r="H1" s="154"/>
+      <c r="H1" s="152"/>
     </row>
     <row r="2" spans="1:8" ht="14.25">
-      <c r="A2" s="134" t="s">
+      <c r="A2" s="141" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="134"/>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134"/>
-      <c r="G2" s="152" t="s">
+      <c r="B2" s="141"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="G2" s="153" t="s">
         <v>132</v>
       </c>
-      <c r="H2" s="153"/>
+      <c r="H2" s="154"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="135" t="s">
+      <c r="A3" s="142" t="s">
         <v>80</v>
       </c>
-      <c r="B3" s="135" t="s">
+      <c r="B3" s="142" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="130" t="s">
+      <c r="C3" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="D3" s="130" t="s">
+      <c r="D3" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="G3" s="151" t="s">
+      <c r="G3" s="56" t="s">
         <v>133</v>
       </c>
-      <c r="H3" s="151" t="s">
+      <c r="H3" s="56" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="136"/>
-      <c r="B4" s="136"/>
-      <c r="C4" s="131" t="s">
+      <c r="A4" s="143"/>
+      <c r="B4" s="143"/>
+      <c r="C4" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="131" t="s">
+      <c r="D4" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="132" t="s">
+      <c r="G4" s="54" t="s">
         <v>135</v>
       </c>
-      <c r="H4" s="132">
+      <c r="H4" s="54">
         <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="132" t="s">
+      <c r="A5" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="132" t="s">
+      <c r="B5" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="132">
+      <c r="C5" s="54">
         <v>0.28999999999999998</v>
       </c>
-      <c r="D5" s="132" t="s">
+      <c r="D5" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="G5" s="132" t="s">
+      <c r="G5" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="H5" s="132">
+      <c r="H5" s="54">
         <v>1.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="133" t="s">
+      <c r="A6" s="55" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="133" t="s">
+      <c r="B6" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="133">
+      <c r="C6" s="55">
         <v>0.57999999999999996</v>
       </c>
-      <c r="D6" s="133" t="s">
+      <c r="D6" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="G6" s="132" t="s">
+      <c r="G6" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="H6" s="132">
+      <c r="H6" s="54">
         <v>1.45</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="133" t="s">
+      <c r="A7" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="133" t="s">
+      <c r="B7" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="133">
+      <c r="C7" s="55">
         <v>0.17</v>
       </c>
-      <c r="D7" s="133" t="s">
+      <c r="D7" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="G7" s="132" t="s">
+      <c r="G7" s="54" t="s">
         <v>138</v>
       </c>
-      <c r="H7" s="132">
+      <c r="H7" s="54">
         <v>1.6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="133" t="s">
+      <c r="A8" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="133" t="s">
+      <c r="B8" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C8" s="133">
+      <c r="C8" s="55">
         <v>0.24</v>
       </c>
-      <c r="D8" s="133" t="s">
+      <c r="D8" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="G8" s="132" t="s">
+      <c r="G8" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="H8" s="132">
+      <c r="H8" s="54">
         <v>1.75</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="133" t="s">
+      <c r="A9" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="133" t="s">
+      <c r="B9" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C9" s="133">
+      <c r="C9" s="55">
         <v>0.06</v>
       </c>
-      <c r="D9" s="133" t="s">
+      <c r="D9" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="132" t="s">
+      <c r="G9" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="H9" s="132">
+      <c r="H9" s="54">
         <v>1.9</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="133" t="s">
+      <c r="A10" s="55" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="133" t="s">
+      <c r="B10" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="133">
+      <c r="C10" s="55">
         <v>0.1</v>
       </c>
-      <c r="D10" s="133" t="s">
+      <c r="D10" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="132" t="s">
+      <c r="G10" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="H10" s="132">
+      <c r="H10" s="54">
         <v>2.0499999999999998</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="132" t="s">
+      <c r="A11" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="132" t="s">
+      <c r="B11" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="132">
+      <c r="C11" s="54">
         <v>0.89</v>
       </c>
-      <c r="D11" s="132" t="s">
+      <c r="D11" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="G11" s="132" t="s">
+      <c r="G11" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="H11" s="132">
+      <c r="H11" s="54">
         <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="132" t="s">
+      <c r="A12" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="B12" s="132" t="s">
+      <c r="B12" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="132">
+      <c r="C12" s="54">
         <v>0.52</v>
       </c>
-      <c r="D12" s="132" t="s">
+      <c r="D12" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="G12" s="132" t="s">
+      <c r="G12" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="H12" s="132">
+      <c r="H12" s="54">
         <v>2.35</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="137"/>
-      <c r="B13" s="137"/>
-      <c r="C13" s="137"/>
-      <c r="D13" s="137"/>
-      <c r="G13" s="132" t="s">
+      <c r="A13" s="149"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="149"/>
+      <c r="D13" s="149"/>
+      <c r="G13" s="54" t="s">
         <v>144</v>
       </c>
-      <c r="H13" s="132">
+      <c r="H13" s="54">
         <v>2.5</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="14.25">
-      <c r="A14" s="134" t="s">
+      <c r="A14" s="141" t="s">
         <v>96</v>
       </c>
-      <c r="B14" s="134"/>
-      <c r="C14" s="134"/>
-      <c r="D14" s="134"/>
-      <c r="G14" s="132" t="s">
+      <c r="B14" s="141"/>
+      <c r="C14" s="141"/>
+      <c r="D14" s="141"/>
+      <c r="G14" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="H14" s="132">
+      <c r="H14" s="54">
         <v>2.65</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="135" t="s">
+      <c r="A15" s="142" t="s">
         <v>80</v>
       </c>
-      <c r="B15" s="135" t="s">
+      <c r="B15" s="142" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="130" t="s">
+      <c r="C15" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="130" t="s">
+      <c r="D15" s="52" t="s">
         <v>84</v>
       </c>
-      <c r="G15" s="132" t="s">
+      <c r="G15" s="54" t="s">
         <v>146</v>
       </c>
-      <c r="H15" s="132">
+      <c r="H15" s="54">
         <v>2.8</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="136"/>
-      <c r="B16" s="136"/>
-      <c r="C16" s="131" t="s">
+      <c r="A16" s="143"/>
+      <c r="B16" s="143"/>
+      <c r="C16" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="D16" s="131" t="s">
+      <c r="D16" s="53" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="132" t="s">
+      <c r="A17" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="B17" s="132" t="s">
+      <c r="B17" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="132">
+      <c r="C17" s="54">
         <v>0.5</v>
       </c>
-      <c r="D17" s="132" t="s">
+      <c r="D17" s="54" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="137"/>
-      <c r="B18" s="137"/>
-      <c r="C18" s="137"/>
-      <c r="D18" s="137"/>
+      <c r="A18" s="149"/>
+      <c r="B18" s="149"/>
+      <c r="C18" s="149"/>
+      <c r="D18" s="149"/>
     </row>
     <row r="19" spans="1:4" ht="14.25">
-      <c r="A19" s="134" t="s">
+      <c r="A19" s="141" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="134"/>
-      <c r="C19" s="134"/>
-      <c r="D19" s="134"/>
+      <c r="B19" s="141"/>
+      <c r="C19" s="141"/>
+      <c r="D19" s="141"/>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="135" t="s">
+      <c r="A20" s="142" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="135" t="s">
+      <c r="B20" s="142" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="130" t="s">
+      <c r="C20" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="130" t="s">
+      <c r="D20" s="52" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="136"/>
-      <c r="B21" s="136"/>
-      <c r="C21" s="131" t="s">
+      <c r="A21" s="143"/>
+      <c r="B21" s="143"/>
+      <c r="C21" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="131" t="s">
+      <c r="D21" s="53" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="133" t="s">
+      <c r="A22" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="133" t="s">
+      <c r="B22" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="133">
+      <c r="C22" s="55">
         <v>1.85</v>
       </c>
-      <c r="D22" s="133" t="s">
+      <c r="D22" s="55" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="133" t="s">
+      <c r="A23" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="133" t="s">
+      <c r="B23" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="133">
+      <c r="C23" s="55">
         <v>0.83</v>
       </c>
-      <c r="D23" s="133" t="s">
+      <c r="D23" s="55" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="133" t="s">
+      <c r="A24" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="133" t="s">
+      <c r="B24" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="133">
+      <c r="C24" s="55">
         <v>0.52</v>
       </c>
-      <c r="D24" s="133" t="s">
+      <c r="D24" s="55" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="133" t="s">
+      <c r="A25" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="B25" s="133" t="s">
+      <c r="B25" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="133">
+      <c r="C25" s="55">
         <v>2.4500000000000002</v>
       </c>
-      <c r="D25" s="133" t="s">
+      <c r="D25" s="55" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="133" t="s">
+      <c r="A26" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="B26" s="133" t="s">
+      <c r="B26" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="133">
+      <c r="C26" s="55">
         <v>0.66</v>
       </c>
-      <c r="D26" s="133" t="s">
+      <c r="D26" s="55" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="133" t="s">
+      <c r="A27" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="133" t="s">
+      <c r="B27" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="133">
+      <c r="C27" s="55">
         <v>0.77</v>
       </c>
-      <c r="D27" s="133" t="s">
+      <c r="D27" s="55" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="133" t="s">
+      <c r="A28" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="B28" s="133" t="s">
+      <c r="B28" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C28" s="133">
+      <c r="C28" s="55">
         <v>0.44</v>
       </c>
-      <c r="D28" s="133" t="s">
+      <c r="D28" s="55" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="133" t="s">
+      <c r="A29" s="55" t="s">
         <v>105</v>
       </c>
-      <c r="B29" s="133" t="s">
+      <c r="B29" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="133">
+      <c r="C29" s="55">
         <v>0.81</v>
       </c>
-      <c r="D29" s="133" t="s">
+      <c r="D29" s="55" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="132" t="s">
+      <c r="A30" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="B30" s="132" t="s">
+      <c r="B30" s="54" t="s">
         <v>107</v>
       </c>
-      <c r="C30" s="132">
+      <c r="C30" s="54">
         <v>0.03</v>
       </c>
-      <c r="D30" s="132" t="s">
+      <c r="D30" s="54" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="133" t="s">
+      <c r="A31" s="55" t="s">
         <v>109</v>
       </c>
-      <c r="B31" s="133" t="s">
+      <c r="B31" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C31" s="133">
+      <c r="C31" s="55">
         <v>1.69</v>
       </c>
-      <c r="D31" s="133" t="s">
+      <c r="D31" s="55" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="133" t="s">
+      <c r="A32" s="55" t="s">
         <v>110</v>
       </c>
-      <c r="B32" s="133" t="s">
+      <c r="B32" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C32" s="133">
+      <c r="C32" s="55">
         <v>0.46</v>
       </c>
-      <c r="D32" s="133" t="s">
+      <c r="D32" s="55" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="133" t="s">
+      <c r="A33" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="B33" s="133" t="s">
+      <c r="B33" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="133">
+      <c r="C33" s="55">
         <v>0.46</v>
       </c>
-      <c r="D33" s="133" t="s">
+      <c r="D33" s="55" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="132" t="s">
+      <c r="A34" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="B34" s="132" t="s">
+      <c r="B34" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C34" s="132">
+      <c r="C34" s="54">
         <v>0.54</v>
       </c>
-      <c r="D34" s="132" t="s">
+      <c r="D34" s="54" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="132" t="s">
+      <c r="A35" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="B35" s="132" t="s">
+      <c r="B35" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C35" s="132">
+      <c r="C35" s="54">
         <v>0.76</v>
       </c>
-      <c r="D35" s="132" t="s">
+      <c r="D35" s="54" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="132" t="s">
+      <c r="A36" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="B36" s="132" t="s">
+      <c r="B36" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C36" s="132">
+      <c r="C36" s="54">
         <v>0.56000000000000005</v>
       </c>
-      <c r="D36" s="132" t="s">
+      <c r="D36" s="54" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="132" t="s">
+      <c r="A37" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="B37" s="132" t="s">
+      <c r="B37" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C37" s="132">
+      <c r="C37" s="54">
         <v>0.8</v>
       </c>
-      <c r="D37" s="132" t="s">
+      <c r="D37" s="54" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="132" t="s">
+      <c r="A38" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="B38" s="132" t="s">
+      <c r="B38" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C38" s="132">
+      <c r="C38" s="54">
         <v>2.12</v>
       </c>
-      <c r="D38" s="132" t="s">
+      <c r="D38" s="54" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="132" t="s">
+      <c r="A39" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="B39" s="132" t="s">
+      <c r="B39" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="132">
+      <c r="C39" s="54">
         <v>0.17</v>
       </c>
-      <c r="D39" s="132" t="s">
+      <c r="D39" s="54" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="132" t="s">
+      <c r="A40" s="54" t="s">
         <v>118</v>
       </c>
-      <c r="B40" s="132" t="s">
+      <c r="B40" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="132">
+      <c r="C40" s="54">
         <v>0.31</v>
       </c>
-      <c r="D40" s="132" t="s">
+      <c r="D40" s="54" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="132" t="s">
+      <c r="A41" s="54" t="s">
         <v>119</v>
       </c>
-      <c r="B41" s="132" t="s">
+      <c r="B41" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="C41" s="132">
+      <c r="C41" s="54">
         <v>0.52</v>
       </c>
-      <c r="D41" s="132" t="s">
+      <c r="D41" s="54" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="132" t="s">
+      <c r="A42" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="B42" s="132" t="s">
+      <c r="B42" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="C42" s="132">
+      <c r="C42" s="54">
         <v>0.64</v>
       </c>
-      <c r="D42" s="132" t="s">
+      <c r="D42" s="54" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="132" t="s">
+      <c r="A43" s="54" t="s">
         <v>122</v>
       </c>
-      <c r="B43" s="132" t="s">
+      <c r="B43" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="C43" s="132">
+      <c r="C43" s="54">
         <v>0.13</v>
       </c>
-      <c r="D43" s="132" t="s">
+      <c r="D43" s="54" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="132" t="s">
+      <c r="A44" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="B44" s="132" t="s">
+      <c r="B44" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="C44" s="132">
+      <c r="C44" s="54">
         <v>0.56000000000000005</v>
       </c>
-      <c r="D44" s="132" t="s">
+      <c r="D44" s="54" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="138"/>
-      <c r="B45" s="137"/>
-      <c r="C45" s="137"/>
-      <c r="D45" s="139"/>
+      <c r="A45" s="150"/>
+      <c r="B45" s="149"/>
+      <c r="C45" s="149"/>
+      <c r="D45" s="151"/>
     </row>
     <row r="46" spans="1:4" ht="14.25">
-      <c r="A46" s="140" t="s">
+      <c r="A46" s="147" t="s">
         <v>124</v>
       </c>
-      <c r="B46" s="134"/>
-      <c r="C46" s="134"/>
-      <c r="D46" s="141"/>
+      <c r="B46" s="141"/>
+      <c r="C46" s="141"/>
+      <c r="D46" s="148"/>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="135" t="s">
+      <c r="A47" s="142" t="s">
         <v>80</v>
       </c>
-      <c r="B47" s="135" t="s">
+      <c r="B47" s="142" t="s">
         <v>81</v>
       </c>
-      <c r="C47" s="130" t="s">
+      <c r="C47" s="52" t="s">
         <v>82</v>
       </c>
-      <c r="D47" s="130" t="s">
+      <c r="D47" s="52" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="136"/>
-      <c r="B48" s="136"/>
-      <c r="C48" s="131" t="s">
+      <c r="A48" s="143"/>
+      <c r="B48" s="143"/>
+      <c r="C48" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="D48" s="131" t="s">
+      <c r="D48" s="53" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="132" t="s">
+      <c r="A49" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="B49" s="132" t="s">
+      <c r="B49" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C49" s="132">
+      <c r="C49" s="54">
         <v>1.66</v>
       </c>
-      <c r="D49" s="132" t="s">
+      <c r="D49" s="54" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="132" t="s">
+      <c r="A50" s="54" t="s">
         <v>126</v>
       </c>
-      <c r="B50" s="132" t="s">
+      <c r="B50" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="C50" s="132">
+      <c r="C50" s="54">
         <v>0.12</v>
       </c>
-      <c r="D50" s="132" t="s">
+      <c r="D50" s="54" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="142" t="s">
+      <c r="A51" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="B51" s="143"/>
-      <c r="C51" s="143"/>
-      <c r="D51" s="144"/>
+      <c r="B51" s="145"/>
+      <c r="C51" s="145"/>
+      <c r="D51" s="146"/>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="145" t="s">
+      <c r="A52" s="138" t="s">
         <v>128</v>
       </c>
-      <c r="B52" s="146"/>
-      <c r="C52" s="146"/>
-      <c r="D52" s="147"/>
+      <c r="B52" s="139"/>
+      <c r="C52" s="139"/>
+      <c r="D52" s="140"/>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="145" t="s">
+      <c r="A53" s="138" t="s">
         <v>129</v>
       </c>
-      <c r="B53" s="146"/>
-      <c r="C53" s="146"/>
-      <c r="D53" s="147"/>
+      <c r="B53" s="139"/>
+      <c r="C53" s="139"/>
+      <c r="D53" s="140"/>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="145" t="s">
+      <c r="A54" s="138" t="s">
         <v>130</v>
       </c>
-      <c r="B54" s="146"/>
-      <c r="C54" s="146"/>
-      <c r="D54" s="147"/>
+      <c r="B54" s="139"/>
+      <c r="C54" s="139"/>
+      <c r="D54" s="140"/>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="148" t="s">
+      <c r="A55" s="135" t="s">
         <v>131</v>
       </c>
-      <c r="B55" s="149"/>
-      <c r="C55" s="149"/>
-      <c r="D55" s="150"/>
+      <c r="B55" s="136"/>
+      <c r="C55" s="136"/>
+      <c r="D55" s="137"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A54:D54"/>
     <mergeCell ref="A2:D2"/>
@@ -5048,13 +5055,6 @@
     <mergeCell ref="A53:D53"/>
     <mergeCell ref="A46:D46"/>
     <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
